--- a/incoming/경제지표.xlsx
+++ b/incoming/경제지표.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K119"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
   </cols>
@@ -600,7 +600,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>$388.0B</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>$-73.3B</v>
       </c>
       <c r="I7" t="str">
         <v>$-73.0B</v>
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>$314.7B</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -679,7 +679,7 @@
         <v>$312.0B</v>
       </c>
       <c r="K8" t="str">
-        <v>$317.7B</v>
+        <v>$317.6B</v>
       </c>
     </row>
     <row r="9">
@@ -705,7 +705,7 @@
         <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>45.1</v>
       </c>
       <c r="I9" t="str">
         <v>47.5</v>
@@ -740,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
       <c r="I10" t="str">
         <v>0.2%</v>
@@ -749,7 +749,7 @@
         <v>0.4%</v>
       </c>
       <c r="K10" t="str">
-        <v>-1.3%</v>
+        <v>-1.1%</v>
       </c>
     </row>
     <row r="11">
@@ -775,16 +775,16 @@
         <v>3</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>7.359M</v>
       </c>
       <c r="I11" t="str">
-        <v>7.45M</v>
+        <v>7.4M</v>
       </c>
       <c r="J11" t="str">
         <v>7.3M</v>
       </c>
       <c r="K11" t="str">
-        <v>7.594M</v>
+        <v>7.537M</v>
       </c>
     </row>
     <row r="12">
@@ -810,10 +810,10 @@
         <v>2</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>2.690M</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>-2M</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -845,7 +845,7 @@
         <v>2</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>44K</v>
       </c>
       <c r="I13" t="str">
         <v>70K</v>
@@ -854,7 +854,7 @@
         <v>90.0K</v>
       </c>
       <c r="K13" t="str">
-        <v>98K</v>
+        <v>95K</v>
       </c>
     </row>
     <row r="14">
@@ -897,7 +897,7 @@
         <v>2026/08/05</v>
       </c>
       <c r="B15" t="str">
-        <v>23:00</v>
+        <v>22:45</v>
       </c>
       <c r="C15" t="str">
         <v>USD</v>
@@ -909,22 +909,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F15" t="str">
-        <v>ISM 서비스업 PMI</v>
+        <v>S&amp;P 서비스업 PMI(확정)</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>54.6</v>
       </c>
       <c r="I15" t="str">
-        <v>54.5</v>
+        <v>53.6</v>
       </c>
       <c r="J15" t="str">
-        <v>54.5</v>
+        <v>53.6</v>
       </c>
       <c r="K15" t="str">
-        <v>54.0</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="16">
@@ -932,7 +932,7 @@
         <v>2026/08/05</v>
       </c>
       <c r="B16" t="str">
-        <v>23:30</v>
+        <v>22:45</v>
       </c>
       <c r="C16" t="str">
         <v>USD</v>
@@ -944,22 +944,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F16" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>S&amp;P 종합 PMI(확정)</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>53.6</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>53.6</v>
       </c>
       <c r="K16" t="str">
-        <v>0.007M</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="17">
@@ -967,7 +967,7 @@
         <v>2026/08/05</v>
       </c>
       <c r="B17" t="str">
-        <v>23:30</v>
+        <v>23:00</v>
       </c>
       <c r="C17" t="str">
         <v>USD</v>
@@ -979,30 +979,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F17" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>ISM 서비스업 PMI</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>54.1</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="K17" t="str">
-        <v>-7.167M</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026/08/06</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B18" t="str">
-        <v>05:05</v>
+        <v>23:30</v>
       </c>
       <c r="C18" t="str">
         <v>USD</v>
@@ -1011,60 +1011,60 @@
         <v>미국</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F18" t="str">
-        <v>Fed Cook 연설</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>-1.643M</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>-1.3M</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>0.007M</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026/08/06</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B19" t="str">
-        <v>18:00</v>
+        <v>23:30</v>
       </c>
       <c r="C19" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D19" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E19" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F19" t="str">
-        <v>소매판매 MoM</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>2.479M</v>
       </c>
       <c r="I19" t="str">
-        <v>0.2%</v>
+        <v>-1.5M</v>
       </c>
       <c r="J19" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>0.2%</v>
+        <v>-7.167M</v>
       </c>
     </row>
     <row r="20">
@@ -1072,7 +1072,7 @@
         <v>2026/08/06</v>
       </c>
       <c r="B20" t="str">
-        <v>21:30</v>
+        <v>05:05</v>
       </c>
       <c r="C20" t="str">
         <v>USD</v>
@@ -1081,10 +1081,10 @@
         <v>미국</v>
       </c>
       <c r="E20" t="str">
-        <v>2026/08/01</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>Fed Cook 연설</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1093,13 +1093,13 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>201K</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>199.0K</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>197K</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1107,34 +1107,34 @@
         <v>2026/08/06</v>
       </c>
       <c r="B21" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C21" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D21" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E21" t="str">
         <v>2026/06/30</v>
       </c>
       <c r="F21" t="str">
-        <v>단위 노동 비용(잠정) QoQ</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
       <c r="I21" t="str">
-        <v>2.0%</v>
+        <v>0.1%</v>
       </c>
       <c r="J21" t="str">
-        <v>2.0%</v>
+        <v>0.1%</v>
       </c>
       <c r="K21" t="str">
-        <v>1.8%</v>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="22">
@@ -1151,33 +1151,33 @@
         <v>미국</v>
       </c>
       <c r="E22" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/01</v>
       </c>
       <c r="F22" t="str">
-        <v>비농업 생산성(잠정) QoQ</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>199K</v>
       </c>
       <c r="I22" t="str">
-        <v>0.6%</v>
+        <v>202K</v>
       </c>
       <c r="J22" t="str">
-        <v>0.6%</v>
+        <v>199.0K</v>
       </c>
       <c r="K22" t="str">
-        <v>0.3%</v>
+        <v>198K</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026/08/07</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B23" t="str">
-        <v>06:30</v>
+        <v>21:30</v>
       </c>
       <c r="C23" t="str">
         <v>USD</v>
@@ -1186,30 +1186,30 @@
         <v>미국</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>2026/06/30</v>
       </c>
       <c r="F23" t="str">
-        <v>Fed Musalem 연설</v>
+        <v>단위 노동 비용(잠정) QoQ</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>1.3%</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2.1%</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>2.0%</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>1.3%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026/08/07</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B24" t="str">
         <v>21:30</v>
@@ -1221,25 +1221,25 @@
         <v>미국</v>
       </c>
       <c r="E24" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F24" t="str">
-        <v>참가율</v>
+        <v>비농업 생산성(잠정) QoQ</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>1.4%</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>0.6%</v>
       </c>
       <c r="J24" t="str">
-        <v>61.6%</v>
+        <v>0.6%</v>
       </c>
       <c r="K24" t="str">
-        <v>61.5%</v>
+        <v>0.8%</v>
       </c>
     </row>
     <row r="25">
@@ -1247,7 +1247,7 @@
         <v>2026/08/07</v>
       </c>
       <c r="B25" t="str">
-        <v>21:30</v>
+        <v>06:30</v>
       </c>
       <c r="C25" t="str">
         <v>USD</v>
@@ -1256,25 +1256,25 @@
         <v>미국</v>
       </c>
       <c r="E25" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>비농업 고용자수</v>
+        <v>Fed Musalem 연설</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="str">
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>83.0K</v>
+        <v/>
       </c>
       <c r="J25" t="str">
-        <v>79.0K</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>57K</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1294,22 +1294,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F26" t="str">
-        <v>시간당 평균소득 YoY</v>
+        <v>참가율</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>61.4%</v>
       </c>
       <c r="I26" t="str">
-        <v>3.5%</v>
+        <v/>
       </c>
       <c r="J26" t="str">
-        <v>3.5%</v>
+        <v>61.6%</v>
       </c>
       <c r="K26" t="str">
-        <v>3.5%</v>
+        <v>61.5%</v>
       </c>
     </row>
     <row r="27">
@@ -1329,22 +1329,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F27" t="str">
-        <v>실업률</v>
+        <v>비농업 고용자수</v>
       </c>
       <c r="G27">
         <v>3</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>-23K</v>
       </c>
       <c r="I27" t="str">
-        <v>4.3%</v>
+        <v>80K</v>
       </c>
       <c r="J27" t="str">
-        <v>4.2%</v>
+        <v>79.0K</v>
       </c>
       <c r="K27" t="str">
-        <v>4.2%</v>
+        <v>20K</v>
       </c>
     </row>
     <row r="28">
@@ -1364,22 +1364,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F28" t="str">
-        <v>시간당 평균 소득 MoM</v>
+        <v>시간당 평균소득 YoY</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>3.2%</v>
       </c>
       <c r="I28" t="str">
-        <v>0.3%</v>
+        <v>3.5%</v>
       </c>
       <c r="J28" t="str">
-        <v>0.3%</v>
+        <v>3.5%</v>
       </c>
       <c r="K28" t="str">
-        <v>0.3%</v>
+        <v>3.4%</v>
       </c>
     </row>
     <row r="29">
@@ -1387,7 +1387,7 @@
         <v>2026/08/07</v>
       </c>
       <c r="B29" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C29" t="str">
         <v>USD</v>
@@ -1396,33 +1396,33 @@
         <v>미국</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F29" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>실업률</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>4.1%</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026/08/11</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B30" t="str">
-        <v>21:15</v>
+        <v>21:30</v>
       </c>
       <c r="C30" t="str">
         <v>USD</v>
@@ -1431,30 +1431,30 @@
         <v>미국</v>
       </c>
       <c r="E30" t="str">
-        <v>2026/07/25</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F30" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>시간당 평균 소득 MoM</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K30" t="str">
-        <v>15.0K</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026/08/11</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B31" t="str">
         <v>23:00</v>
@@ -1466,10 +1466,10 @@
         <v>미국</v>
       </c>
       <c r="E31" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v>기존주택 판매</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1481,18 +1481,18 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v>4.06M</v>
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>4.09M</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026/08/11</v>
+        <v>2026/08/09</v>
       </c>
       <c r="B32" t="str">
-        <v>23:00</v>
+        <v>01:45</v>
       </c>
       <c r="C32" t="str">
         <v>USD</v>
@@ -1501,10 +1501,10 @@
         <v>미국</v>
       </c>
       <c r="E32" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v>기존주택 판매 MoM</v>
+        <v>Fed Bowman 연설</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1516,18 +1516,18 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>-0.7%</v>
+        <v/>
       </c>
       <c r="K32" t="str">
-        <v>-2.4%</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026/08/12</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B33" t="str">
-        <v>05:30</v>
+        <v>04:00</v>
       </c>
       <c r="C33" t="str">
         <v>USD</v>
@@ -1536,10 +1536,10 @@
         <v>미국</v>
       </c>
       <c r="E33" t="str">
-        <v>2026/08/07</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>Fed Hammack 연설</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026/08/12</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B34" t="str">
-        <v>21:30</v>
+        <v>21:15</v>
       </c>
       <c r="C34" t="str">
         <v>USD</v>
@@ -1571,33 +1571,33 @@
         <v>미국</v>
       </c>
       <c r="E34" t="str">
-        <v>2026/07/31</v>
+        <v>2026/07/25</v>
       </c>
       <c r="F34" t="str">
-        <v>소비자물가지수-계절조정</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G34">
         <v>2</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>8.25K</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>332.6</v>
+        <v/>
       </c>
       <c r="K34" t="str">
-        <v>332.568</v>
+        <v>11.0K</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026/08/12</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B35" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C35" t="str">
         <v>USD</v>
@@ -1609,30 +1609,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F35" t="str">
-        <v>CPI상승률 YoY</v>
+        <v>기존주택 판매</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>4.06M</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>4.05M</v>
       </c>
       <c r="J35" t="str">
-        <v>3.4%</v>
+        <v>4.06M</v>
       </c>
       <c r="K35" t="str">
-        <v>3.5%</v>
+        <v>4.13M</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026/08/12</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B36" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C36" t="str">
         <v>USD</v>
@@ -1644,22 +1644,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F36" t="str">
-        <v>근원 CPI상승률 MoM</v>
+        <v>기존주택 판매 MoM</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>-1.7%</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>0.2%</v>
+        <v>-0.7%</v>
       </c>
       <c r="K36" t="str">
-        <v>0%</v>
+        <v>-1.4%</v>
       </c>
     </row>
     <row r="37">
@@ -1667,7 +1667,7 @@
         <v>2026/08/12</v>
       </c>
       <c r="B37" t="str">
-        <v>21:30</v>
+        <v>05:30</v>
       </c>
       <c r="C37" t="str">
         <v>USD</v>
@@ -1676,25 +1676,25 @@
         <v>미국</v>
       </c>
       <c r="E37" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/07</v>
       </c>
       <c r="F37" t="str">
-        <v>근원 CPI상승률 YoY</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>9.072M</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>-0.50M</v>
       </c>
       <c r="J37" t="str">
-        <v>2.5%</v>
+        <v/>
       </c>
       <c r="K37" t="str">
-        <v>2.6%</v>
+        <v>2.69M</v>
       </c>
     </row>
     <row r="38">
@@ -1714,22 +1714,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F38" t="str">
-        <v>CPI상승률 MoM</v>
+        <v>소비자물가지수-계절조정</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>332.81</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>0.0%</v>
+        <v>332.6</v>
       </c>
       <c r="K38" t="str">
-        <v>-0.4%</v>
+        <v>332.57</v>
       </c>
     </row>
     <row r="39">
@@ -1749,22 +1749,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F39" t="str">
-        <v>소비자물가지수</v>
+        <v>CPI상승률 YoY</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>3.4%</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>3.4%</v>
       </c>
       <c r="J39" t="str">
-        <v>334.03</v>
+        <v>3.4%</v>
       </c>
       <c r="K39" t="str">
-        <v>333.95</v>
+        <v>3.5%</v>
       </c>
     </row>
     <row r="40">
@@ -1772,7 +1772,7 @@
         <v>2026/08/12</v>
       </c>
       <c r="B40" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C40" t="str">
         <v>USD</v>
@@ -1781,25 +1781,25 @@
         <v>미국</v>
       </c>
       <c r="E40" t="str">
-        <v>2026/08/07</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F40" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>근원 CPI상승률 MoM</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>0%</v>
       </c>
     </row>
     <row r="41">
@@ -1807,7 +1807,7 @@
         <v>2026/08/12</v>
       </c>
       <c r="B41" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C41" t="str">
         <v>USD</v>
@@ -1816,33 +1816,33 @@
         <v>미국</v>
       </c>
       <c r="E41" t="str">
-        <v>2026/08/07</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F41" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>근원 CPI상승률 YoY</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>2.6%</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026/08/13</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B42" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C42" t="str">
         <v>USD</v>
@@ -1851,33 +1851,33 @@
         <v>미국</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F42" t="str">
-        <v>국채 입찰(10Y Note)</v>
+        <v>CPI상승률 MoM</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>0.0%</v>
       </c>
       <c r="K42" t="str">
-        <v>4.580%</v>
+        <v>-0.4%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026/08/13</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B43" t="str">
-        <v>03:00</v>
+        <v>21:30</v>
       </c>
       <c r="C43" t="str">
         <v>USD</v>
@@ -1889,65 +1889,65 @@
         <v>2026/07/31</v>
       </c>
       <c r="F43" t="str">
-        <v>월간 예산 성명서</v>
+        <v>소비자물가지수</v>
       </c>
       <c r="G43">
         <v>2</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>333.92</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>333.99</v>
       </c>
       <c r="J43" t="str">
-        <v>$-340.0B</v>
+        <v>334.03</v>
       </c>
       <c r="K43" t="str">
-        <v>$-120B</v>
+        <v>333.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026/08/13</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B44" t="str">
-        <v>18:00</v>
+        <v>23:30</v>
       </c>
       <c r="C44" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D44" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E44" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/07</v>
       </c>
       <c r="F44" t="str">
-        <v>산업생산 MoM</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G44">
         <v>2</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>-0.968M</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>-1.2M</v>
       </c>
       <c r="J44" t="str">
-        <v>-0.6%</v>
+        <v/>
       </c>
       <c r="K44" t="str">
-        <v>-0.2%</v>
+        <v>-1.643M</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026/08/13</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B45" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -1956,25 +1956,25 @@
         <v>미국</v>
       </c>
       <c r="E45" t="str">
-        <v>2026/08/08</v>
+        <v>2026/08/07</v>
       </c>
       <c r="F45" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>17.422M</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>-1.4M</v>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>2.479M</v>
       </c>
     </row>
     <row r="46">
@@ -1982,7 +1982,7 @@
         <v>2026/08/13</v>
       </c>
       <c r="B46" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -1991,25 +1991,25 @@
         <v>미국</v>
       </c>
       <c r="E46" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>근원 PPI MoM</v>
+        <v>국채 입찰(10Y Note)</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>4.683%</v>
       </c>
       <c r="I46" t="str">
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="K46" t="str">
-        <v>0.2%</v>
+        <v>4.580%</v>
       </c>
     </row>
     <row r="47">
@@ -2017,7 +2017,7 @@
         <v>2026/08/13</v>
       </c>
       <c r="B47" t="str">
-        <v>21:30</v>
+        <v>03:00</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -2029,22 +2029,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F47" t="str">
-        <v>PPI MoM</v>
+        <v>월간 예산 성명서</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>$-432B</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>$-346B</v>
       </c>
       <c r="J47" t="str">
-        <v>-0.1%</v>
+        <v>$-340.0B</v>
       </c>
       <c r="K47" t="str">
-        <v>-0.3%</v>
+        <v>$-120B</v>
       </c>
     </row>
     <row r="48">
@@ -2052,42 +2052,42 @@
         <v>2026/08/13</v>
       </c>
       <c r="B48" t="str">
-        <v>21:40</v>
+        <v>18:00</v>
       </c>
       <c r="C48" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D48" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>2026/06/30</v>
       </c>
       <c r="F48" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B49" t="str">
-        <v>02:00</v>
+        <v>21:15</v>
       </c>
       <c r="C49" t="str">
         <v>USD</v>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>국채 입찰(30Y Bond)</v>
+        <v>Fed Hammack 연설</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2119,127 +2119,127 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B50" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C50" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D50" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E50" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/08</v>
       </c>
       <c r="F50" t="str">
-        <v>GDP 성장률(2차 추정) QoQ</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>209K</v>
       </c>
       <c r="I50" t="str">
-        <v>0.4%</v>
+        <v>202K</v>
       </c>
       <c r="J50" t="str">
-        <v>0.4%</v>
+        <v>204.0K</v>
       </c>
       <c r="K50" t="str">
-        <v>0.0%</v>
+        <v>200K</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B51" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C51" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D51" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E51" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F51" t="str">
-        <v>고용 증감(잠정) QoQ</v>
+        <v>근원 PPI MoM</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J51" t="str">
-        <v>0.1%</v>
+        <v>0.2%</v>
       </c>
       <c r="K51" t="str">
-        <v>0.1%</v>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B52" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C52" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D52" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E52" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F52" t="str">
-        <v>GDP 성장률(2차 추정) YoY</v>
+        <v>PPI MoM</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I52" t="str">
-        <v>1%</v>
+        <v>0.2%</v>
       </c>
       <c r="J52" t="str">
-        <v>1.0%</v>
+        <v>0.1%</v>
       </c>
       <c r="K52" t="str">
-        <v>0.5%</v>
+        <v>-0.1%</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B53" t="str">
-        <v>18:00</v>
+        <v>21:40</v>
       </c>
       <c r="C53" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D53" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E53" t="str">
-        <v>2026/06/30</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>무역수지</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2251,10 +2251,10 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>€ 5B</v>
+        <v/>
       </c>
       <c r="K53" t="str">
-        <v>€-7.8B</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2262,7 +2262,7 @@
         <v>2026/08/14</v>
       </c>
       <c r="B54" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C54" t="str">
         <v>USD</v>
@@ -2271,25 +2271,25 @@
         <v>미국</v>
       </c>
       <c r="E54" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v>소매판매 MoM</v>
+        <v>국채 입찰(30Y Bond)</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>5.216%</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>0.5%</v>
+        <v/>
       </c>
       <c r="K54" t="str">
-        <v>0.2%</v>
+        <v>5.058%</v>
       </c>
     </row>
     <row r="55">
@@ -2297,34 +2297,34 @@
         <v>2026/08/14</v>
       </c>
       <c r="B55" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C55" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D55" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E55" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F55" t="str">
-        <v>미시간대 Consumer Sentiment(잠정)</v>
+        <v>GDP 성장률(2차 추정) QoQ</v>
       </c>
       <c r="G55">
         <v>2</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="J55" t="str">
-        <v>54.6</v>
+        <v>0.4%</v>
       </c>
       <c r="K55" t="str">
-        <v>55.2</v>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="56">
@@ -2332,112 +2332,112 @@
         <v>2026/08/14</v>
       </c>
       <c r="B56" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C56" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D56" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E56" t="str">
         <v>2026/06/30</v>
       </c>
       <c r="F56" t="str">
-        <v>기업 재고 MoM</v>
+        <v>고용 증감(잠정) QoQ</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J56" t="str">
-        <v>-0.2%</v>
+        <v>0.1%</v>
       </c>
       <c r="K56" t="str">
-        <v>0.3%</v>
+        <v>0.1%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026/08/17</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B57" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C57" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D57" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E57" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F57" t="str">
-        <v>뉴욕 엠파이어스테이트 제조업지수</v>
+        <v>GDP 성장률(2차 추정) YoY</v>
       </c>
       <c r="G57">
         <v>2</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>1%</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>1%</v>
       </c>
       <c r="J57" t="str">
-        <v>12</v>
+        <v>1.0%</v>
       </c>
       <c r="K57" t="str">
-        <v>15.60</v>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026/08/17</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B58" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D58" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E58" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F58" t="str">
-        <v>NAHB 주택 시장지수</v>
+        <v>무역수지</v>
       </c>
       <c r="G58">
         <v>2</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>€8.6B</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>€-2.2B</v>
       </c>
       <c r="J58" t="str">
-        <v>34</v>
+        <v>€ 5B</v>
       </c>
       <c r="K58" t="str">
-        <v>34</v>
+        <v>€-9B</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026/08/18</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B59" t="str">
-        <v>05:00</v>
+        <v>21:30</v>
       </c>
       <c r="C59" t="str">
         <v>USD</v>
@@ -2446,68 +2446,68 @@
         <v>미국</v>
       </c>
       <c r="E59" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F59" t="str">
-        <v>장기 TIC 순 유출입</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>-0.6%</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K59" t="str">
-        <v>$232.7B</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026/08/18</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B60" t="str">
-        <v>18:00</v>
+        <v>23:00</v>
       </c>
       <c r="C60" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D60" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E60" t="str">
         <v>2026/08/31</v>
       </c>
       <c r="F60" t="str">
-        <v>ZEW 경제심리지수</v>
+        <v>미시간대 Consumer Sentiment(잠정)</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>51.0</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="J60" t="str">
-        <v>20</v>
+        <v>54.6</v>
       </c>
       <c r="K60" t="str">
-        <v>23.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026/08/18</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B61" t="str">
-        <v>21:15</v>
+        <v>23:00</v>
       </c>
       <c r="C61" t="str">
         <v>USD</v>
@@ -2516,30 +2516,30 @@
         <v>미국</v>
       </c>
       <c r="E61" t="str">
-        <v>2026/08/01</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F61" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>기업 재고 MoM</v>
       </c>
       <c r="G61">
         <v>2</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026/08/18</v>
+        <v>2026/08/17</v>
       </c>
       <c r="B62" t="str">
         <v>21:30</v>
@@ -2551,33 +2551,33 @@
         <v>미국</v>
       </c>
       <c r="E62" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F62" t="str">
-        <v>주택 착공 MoM</v>
+        <v>뉴욕 엠파이어스테이트 제조업지수</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>20.60</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="J62" t="str">
-        <v>-4.7%</v>
+        <v>12</v>
       </c>
       <c r="K62" t="str">
-        <v>19%</v>
+        <v>15.60</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026/08/18</v>
+        <v>2026/08/17</v>
       </c>
       <c r="B63" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C63" t="str">
         <v>USD</v>
@@ -2586,25 +2586,25 @@
         <v>미국</v>
       </c>
       <c r="E63" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F63" t="str">
-        <v>주택 착공</v>
+        <v>NAHB 주택 시장지수</v>
       </c>
       <c r="G63">
         <v>2</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>35</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>33</v>
       </c>
       <c r="J63" t="str">
-        <v>1.36M</v>
+        <v>34</v>
       </c>
       <c r="K63" t="str">
-        <v>1.427M</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
@@ -2612,7 +2612,7 @@
         <v>2026/08/18</v>
       </c>
       <c r="B64" t="str">
-        <v>21:30</v>
+        <v>05:00</v>
       </c>
       <c r="C64" t="str">
         <v>USD</v>
@@ -2621,25 +2621,25 @@
         <v>미국</v>
       </c>
       <c r="E64" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F64" t="str">
-        <v>수입가격 MoM</v>
+        <v>장기 TIC 순 유출입</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>$172.7B</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>$151.4B</v>
       </c>
       <c r="J64" t="str">
-        <v>0.4%</v>
+        <v/>
       </c>
       <c r="K64" t="str">
-        <v>0.3%</v>
+        <v>$231.2B</v>
       </c>
     </row>
     <row r="65">
@@ -2647,34 +2647,34 @@
         <v>2026/08/18</v>
       </c>
       <c r="B65" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E65" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F65" t="str">
-        <v>수출가격 MoM</v>
+        <v>ZEW 경제심리지수</v>
       </c>
       <c r="G65">
         <v>2</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>31.4</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>25.4</v>
       </c>
       <c r="J65" t="str">
-        <v>-0.2%</v>
+        <v>24</v>
       </c>
       <c r="K65" t="str">
-        <v>-0.6%</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="66">
@@ -2682,7 +2682,7 @@
         <v>2026/08/18</v>
       </c>
       <c r="B66" t="str">
-        <v>22:15</v>
+        <v>21:15</v>
       </c>
       <c r="C66" t="str">
         <v>USD</v>
@@ -2691,25 +2691,25 @@
         <v>미국</v>
       </c>
       <c r="E66" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/01</v>
       </c>
       <c r="F66" t="str">
-        <v>산업생산 MoM</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G66">
         <v>2</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>9.5K</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="K66" t="str">
-        <v>0.1%</v>
+        <v>8.25K</v>
       </c>
     </row>
     <row r="67">
@@ -2717,7 +2717,7 @@
         <v>2026/08/18</v>
       </c>
       <c r="B67" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C67" t="str">
         <v>USD</v>
@@ -2729,22 +2729,22 @@
         <v>2026/07/31</v>
       </c>
       <c r="F67" t="str">
-        <v>잠정 주택 판매 MoM</v>
+        <v>주택 착공 MoM</v>
       </c>
       <c r="G67">
         <v>2</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>-12.4%</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>1.9%</v>
+        <v>-4.7%</v>
       </c>
       <c r="K67" t="str">
-        <v>-5.4%</v>
+        <v>19.7%</v>
       </c>
     </row>
     <row r="68">
@@ -2752,7 +2752,7 @@
         <v>2026/08/18</v>
       </c>
       <c r="B68" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C68" t="str">
         <v>USD</v>
@@ -2764,30 +2764,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F68" t="str">
-        <v>잠정주택 판매 YoY</v>
+        <v>주택 착공</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>1.239M</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>1.35M</v>
       </c>
       <c r="J68" t="str">
-        <v>1.4%</v>
+        <v>1.36M</v>
       </c>
       <c r="K68" t="str">
-        <v>-0.3%</v>
+        <v>1.415M</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026/08/19</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B69" t="str">
-        <v>05:30</v>
+        <v>21:30</v>
       </c>
       <c r="C69" t="str">
         <v>USD</v>
@@ -2796,68 +2796,68 @@
         <v>미국</v>
       </c>
       <c r="E69" t="str">
-        <v>2026/08/14</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F69" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>수입가격 MoM</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>-0.4%</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026/08/19</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B70" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C70" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D70" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E70" t="str">
         <v>2026/07/31</v>
       </c>
       <c r="F70" t="str">
-        <v>CPI상승률(확정) YoY</v>
+        <v>수출가격 MoM</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>-1.3%</v>
       </c>
       <c r="I70" t="str">
-        <v>2.9%</v>
+        <v>0.2%</v>
       </c>
       <c r="J70" t="str">
-        <v>2.9%</v>
+        <v>0.3%</v>
       </c>
       <c r="K70" t="str">
-        <v>2.8%</v>
+        <v>-0.7%</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026/08/19</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B71" t="str">
-        <v>23:30</v>
+        <v>22:15</v>
       </c>
       <c r="C71" t="str">
         <v>USD</v>
@@ -2866,33 +2866,33 @@
         <v>미국</v>
       </c>
       <c r="E71" t="str">
-        <v>2026/08/14</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F71" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G71">
         <v>2</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026/08/19</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B72" t="str">
-        <v>23:30</v>
+        <v>23:00</v>
       </c>
       <c r="C72" t="str">
         <v>USD</v>
@@ -2901,33 +2901,33 @@
         <v>미국</v>
       </c>
       <c r="E72" t="str">
-        <v>2026/08/14</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F72" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>잠정 주택 판매 MoM</v>
       </c>
       <c r="G72">
         <v>2</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>-2.3%</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>0.9%</v>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>-4.8%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026/08/20</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B73" t="str">
-        <v>03:00</v>
+        <v>23:00</v>
       </c>
       <c r="C73" t="str">
         <v>USD</v>
@@ -2936,33 +2936,33 @@
         <v>미국</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F73" t="str">
-        <v>FOMC 회의록</v>
+        <v>잠정주택 판매 YoY</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>-2.2%</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>1.4%</v>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026/08/20</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B74" t="str">
-        <v>21:30</v>
+        <v>06:00</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -2971,16 +2971,16 @@
         <v>미국</v>
       </c>
       <c r="E74" t="str">
-        <v>2026/08/15</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F74" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>-3.28M</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2989,27 +2989,27 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>9.072M</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026/08/20</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B75" t="str">
-        <v>21:30</v>
+        <v>16:10</v>
       </c>
       <c r="C75" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D75" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E75" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F75" t="str">
-        <v>필라델피아 연준 제조업지수</v>
+        <v>ECB 총재 Lagarde 연설</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -3021,15 +3021,15 @@
         <v/>
       </c>
       <c r="J75" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="K75" t="str">
-        <v>41.4</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026/08/21</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B76" t="str">
         <v>18:00</v>
@@ -3041,33 +3041,33 @@
         <v>유로 지역</v>
       </c>
       <c r="E76" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F76" t="str">
-        <v>협상 임금 인상률</v>
+        <v>CPI상승률(확정) YoY</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>2.9%</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>2.9%</v>
       </c>
       <c r="J76" t="str">
-        <v>2.5%</v>
+        <v>2.9%</v>
       </c>
       <c r="K76" t="str">
-        <v>2.46%</v>
+        <v>2.8%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026/08/24</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B77" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C77" t="str">
         <v>USD</v>
@@ -3076,33 +3076,33 @@
         <v>미국</v>
       </c>
       <c r="E77" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F77" t="str">
-        <v>시카고 연준 국가 활동지수</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>4.405M</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>-0.6M</v>
       </c>
       <c r="J77" t="str">
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="K77" t="str">
-        <v>-0.02</v>
+        <v>17.422M</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B78" t="str">
-        <v>21:15</v>
+        <v>23:30</v>
       </c>
       <c r="C78" t="str">
         <v>USD</v>
@@ -3111,33 +3111,33 @@
         <v>미국</v>
       </c>
       <c r="E78" t="str">
-        <v>2026/08/08</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F78" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>0.688M</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>-1.2M</v>
       </c>
       <c r="J78" t="str">
         <v/>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>-0.968M</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B79" t="str">
-        <v>22:00</v>
+        <v>03:00</v>
       </c>
       <c r="C79" t="str">
         <v>USD</v>
@@ -3146,13 +3146,13 @@
         <v>미국</v>
       </c>
       <c r="E79" t="str">
-        <v>2026/06/30</v>
+        <v/>
       </c>
       <c r="F79" t="str">
-        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
+        <v>FOMC 회의록</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3161,30 +3161,30 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v>2.1%</v>
+        <v/>
       </c>
       <c r="K79" t="str">
-        <v>1.6%</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B80" t="str">
-        <v>22:00</v>
+        <v>20:30</v>
       </c>
       <c r="C80" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D80" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E80" t="str">
-        <v>2026/06/30</v>
+        <v/>
       </c>
       <c r="F80" t="str">
-        <v>S&amp;P/Case-Shiller 주택가격 MoM</v>
+        <v>ECB 통화 정책 회의</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -3196,18 +3196,18 @@
         <v/>
       </c>
       <c r="J80" t="str">
-        <v>0.5%</v>
+        <v/>
       </c>
       <c r="K80" t="str">
-        <v>0.9%</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B81" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C81" t="str">
         <v>USD</v>
@@ -3216,33 +3216,33 @@
         <v>미국</v>
       </c>
       <c r="E81" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/15</v>
       </c>
       <c r="F81" t="str">
-        <v>신규주택 판매</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G81">
         <v>2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>206K</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>210K</v>
       </c>
       <c r="J81" t="str">
-        <v>0.62M</v>
+        <v>201.0K</v>
       </c>
       <c r="K81" t="str">
-        <v>0.628M</v>
+        <v>212K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B82" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C82" t="str">
         <v>USD</v>
@@ -3251,68 +3251,68 @@
         <v>미국</v>
       </c>
       <c r="E82" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F82" t="str">
-        <v>신규주택 판매 MoM</v>
+        <v>필라델피아 연준 제조업지수</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>47.4</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="J82" t="str">
-        <v>-1.3%</v>
+        <v>25</v>
       </c>
       <c r="K82" t="str">
-        <v>1.6%</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026/08/25</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B83" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C83" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D83" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E83" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F83" t="str">
-        <v>CB 소비자 신뢰지수</v>
+        <v>협상 임금 인상률</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>2.44%</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>90.9</v>
+        <v>2.5%</v>
       </c>
       <c r="K83" t="str">
-        <v>90.8</v>
+        <v>2.56%</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B84" t="str">
-        <v>05:30</v>
+        <v>22:45</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -3321,33 +3321,33 @@
         <v>미국</v>
       </c>
       <c r="E84" t="str">
-        <v>2026/08/21</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F84" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>S&amp;P 서비스업 PMI(속보)</v>
       </c>
       <c r="G84">
         <v>2</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>56.8</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>54</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>53.8</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>54.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B85" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -3356,33 +3356,33 @@
         <v>미국</v>
       </c>
       <c r="E85" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F85" t="str">
-        <v>개인 지출 MoM</v>
+        <v>S&amp;P 제조업 PMI(속보)</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>53.2</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>53.9</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>53.5</v>
       </c>
       <c r="K85" t="str">
-        <v>0.3%</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B86" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C86" t="str">
         <v>USD</v>
@@ -3391,30 +3391,30 @@
         <v>미국</v>
       </c>
       <c r="E86" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F86" t="str">
-        <v>기업 이익(잠정) QoQ</v>
+        <v>S&amp;P 종합 PMI(속보)</v>
       </c>
       <c r="G86">
         <v>2</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>56.0</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>53.2</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/24</v>
       </c>
       <c r="B87" t="str">
         <v>21:30</v>
@@ -3429,10 +3429,10 @@
         <v>2026/07/31</v>
       </c>
       <c r="F87" t="str">
-        <v>개인 소득 MoM</v>
+        <v>시카고 연준 국가 활동지수</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -3441,18 +3441,18 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="K87" t="str">
-        <v>0.2%</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B88" t="str">
-        <v>21:30</v>
+        <v>21:00</v>
       </c>
       <c r="C88" t="str">
         <v>USD</v>
@@ -3461,10 +3461,10 @@
         <v>미국</v>
       </c>
       <c r="E88" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v>PCE 물가지수 MoM</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -3479,15 +3479,15 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>-0.1%</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B89" t="str">
-        <v>21:30</v>
+        <v>21:15</v>
       </c>
       <c r="C89" t="str">
         <v>USD</v>
@@ -3496,10 +3496,10 @@
         <v>미국</v>
       </c>
       <c r="E89" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/08</v>
       </c>
       <c r="F89" t="str">
-        <v>내구재 주문(운송 제외) MoM</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G89">
         <v>2</v>
@@ -3514,15 +3514,15 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>0.6%</v>
+        <v>9.5K</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B90" t="str">
-        <v>21:30</v>
+        <v>22:00</v>
       </c>
       <c r="C90" t="str">
         <v>USD</v>
@@ -3531,33 +3531,33 @@
         <v>미국</v>
       </c>
       <c r="E90" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F90" t="str">
-        <v>내구재 주문 MoM</v>
+        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" t="str">
         <v/>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>1.7%</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>1.8%</v>
       </c>
       <c r="K90" t="str">
-        <v>0.3%</v>
+        <v>1.6%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B91" t="str">
-        <v>21:30</v>
+        <v>22:00</v>
       </c>
       <c r="C91" t="str">
         <v>USD</v>
@@ -3569,7 +3569,7 @@
         <v>2026/06/30</v>
       </c>
       <c r="F91" t="str">
-        <v>GDP 물가지수(2차 예측) QoQ</v>
+        <v>S&amp;P/Case-Shiller 주택가격 MoM</v>
       </c>
       <c r="G91">
         <v>2</v>
@@ -3578,21 +3578,21 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v>6.3%</v>
+        <v/>
       </c>
       <c r="J91" t="str">
-        <v>6.3%</v>
+        <v>0.4%</v>
       </c>
       <c r="K91" t="str">
-        <v>3.6%</v>
+        <v>0.9%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B92" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C92" t="str">
         <v>USD</v>
@@ -3604,7 +3604,7 @@
         <v>2026/07/31</v>
       </c>
       <c r="F92" t="str">
-        <v>PCE 물가지수 YoY</v>
+        <v>신규주택 판매</v>
       </c>
       <c r="G92">
         <v>2</v>
@@ -3613,21 +3613,21 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>0.62M</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>0.62M</v>
       </c>
       <c r="K92" t="str">
-        <v>3.7%</v>
+        <v>0.628M</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B93" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C93" t="str">
         <v>USD</v>
@@ -3639,10 +3639,10 @@
         <v>2026/07/31</v>
       </c>
       <c r="F93" t="str">
-        <v>근원 PCE 물가지수 MoM</v>
+        <v>신규주택 판매 MoM</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -3651,18 +3651,18 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v/>
+        <v>-1.3%</v>
       </c>
       <c r="K93" t="str">
-        <v>0.1%</v>
+        <v>1.6%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026/08/26</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B94" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C94" t="str">
         <v>USD</v>
@@ -3671,25 +3671,25 @@
         <v>미국</v>
       </c>
       <c r="E94" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F94" t="str">
-        <v>GDP성장률(2차 예측) QoQ</v>
+        <v>CB 소비자 신뢰지수</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94" t="str">
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>1.5%</v>
+        <v>91.2</v>
       </c>
       <c r="J94" t="str">
-        <v>1.5%</v>
+        <v>90.9</v>
       </c>
       <c r="K94" t="str">
-        <v>2.1%</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="95">
@@ -3697,7 +3697,7 @@
         <v>2026/08/26</v>
       </c>
       <c r="B95" t="str">
-        <v>23:30</v>
+        <v>05:00</v>
       </c>
       <c r="C95" t="str">
         <v>USD</v>
@@ -3706,10 +3706,10 @@
         <v>미국</v>
       </c>
       <c r="E95" t="str">
-        <v>2026/08/21</v>
+        <v/>
       </c>
       <c r="F95" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G95">
         <v>2</v>
@@ -3732,7 +3732,7 @@
         <v>2026/08/26</v>
       </c>
       <c r="B96" t="str">
-        <v>23:30</v>
+        <v>05:30</v>
       </c>
       <c r="C96" t="str">
         <v>USD</v>
@@ -3744,7 +3744,7 @@
         <v>2026/08/21</v>
       </c>
       <c r="F96" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -3759,15 +3759,15 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>-3.28M</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026/08/27</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B97" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C97" t="str">
         <v>USD</v>
@@ -3776,33 +3776,33 @@
         <v>미국</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F97" t="str">
-        <v>국채 입찰(2년 FRN)</v>
+        <v>개인 지출 MoM</v>
       </c>
       <c r="G97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H97" t="str">
         <v/>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J97" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K97" t="str">
-        <v>0.050%</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026/08/27</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B98" t="str">
-        <v>09:00</v>
+        <v>21:30</v>
       </c>
       <c r="C98" t="str">
         <v>USD</v>
@@ -3811,10 +3811,10 @@
         <v>미국</v>
       </c>
       <c r="E98" t="str">
-        <v/>
+        <v>2026/06/30</v>
       </c>
       <c r="F98" t="str">
-        <v>Jackson Hole 심포지엄</v>
+        <v>기업 이익(잠정) QoQ</v>
       </c>
       <c r="G98">
         <v>2</v>
@@ -3826,15 +3826,15 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>0.7%</v>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026/08/27</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B99" t="str">
         <v>21:30</v>
@@ -3846,33 +3846,33 @@
         <v>미국</v>
       </c>
       <c r="E99" t="str">
-        <v>2026/08/22</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F99" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>개인 소득 MoM</v>
       </c>
       <c r="G99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" t="str">
         <v/>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026/08/28</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B100" t="str">
-        <v>09:00</v>
+        <v>21:30</v>
       </c>
       <c r="C100" t="str">
         <v>USD</v>
@@ -3881,10 +3881,10 @@
         <v>미국</v>
       </c>
       <c r="E100" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F100" t="str">
-        <v>Jackson Hole 심포지엄</v>
+        <v>PCE 물가지수 MoM</v>
       </c>
       <c r="G100">
         <v>2</v>
@@ -3893,33 +3893,33 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K100" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026/08/28</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B101" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C101" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D101" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E101" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F101" t="str">
-        <v>경제 심리지수</v>
+        <v>내구재 주문(운송 제외) MoM</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -3928,21 +3928,21 @@
         <v/>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>0.5%</v>
       </c>
       <c r="J101" t="str">
-        <v>96.4</v>
+        <v>0.3%</v>
       </c>
       <c r="K101" t="str">
-        <v>96.9</v>
+        <v>0.6%</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026/08/28</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B102" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C102" t="str">
         <v>USD</v>
@@ -3951,33 +3951,33 @@
         <v>미국</v>
       </c>
       <c r="E102" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F102" t="str">
-        <v>시카고 PMI</v>
+        <v>내구재 주문 MoM</v>
       </c>
       <c r="G102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H102" t="str">
         <v/>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>0.7%</v>
       </c>
       <c r="J102" t="str">
-        <v>56.1</v>
+        <v>0.5%</v>
       </c>
       <c r="K102" t="str">
-        <v>57.6</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026/08/28</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B103" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C103" t="str">
         <v>USD</v>
@@ -3986,10 +3986,10 @@
         <v>미국</v>
       </c>
       <c r="E103" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F103" t="str">
-        <v>미시간대 Consumer Sentiment(확정)</v>
+        <v>GDP 물가지수(2차 예측) QoQ</v>
       </c>
       <c r="G103">
         <v>2</v>
@@ -3998,21 +3998,21 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>6.3%</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>6.3%</v>
       </c>
       <c r="K103" t="str">
-        <v>55.2</v>
+        <v>3.6%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026/08/29</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B104" t="str">
-        <v>09:00</v>
+        <v>21:30</v>
       </c>
       <c r="C104" t="str">
         <v>USD</v>
@@ -4021,10 +4021,10 @@
         <v>미국</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F104" t="str">
-        <v>Jackson Hole 심포지엄</v>
+        <v>PCE 물가지수 YoY</v>
       </c>
       <c r="G104">
         <v>2</v>
@@ -4036,50 +4036,540 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>3.7%</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>3.7%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>2026/08/26</v>
+      </c>
+      <c r="B105" t="str">
+        <v>21:30</v>
+      </c>
+      <c r="C105" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D105" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E105" t="str">
+        <v>2026/07/31</v>
+      </c>
+      <c r="F105" t="str">
+        <v>근원 PCE 물가지수 MoM</v>
+      </c>
+      <c r="G105">
+        <v>3</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v>0.2%</v>
+      </c>
+      <c r="J105" t="str">
+        <v>0.3%</v>
+      </c>
+      <c r="K105" t="str">
+        <v>0.1%</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2026/08/26</v>
+      </c>
+      <c r="B106" t="str">
+        <v>21:30</v>
+      </c>
+      <c r="C106" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D106" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2026/06/30</v>
+      </c>
+      <c r="F106" t="str">
+        <v>GDP성장률(2차 예측) QoQ</v>
+      </c>
+      <c r="G106">
+        <v>3</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="J106" t="str">
+        <v>1.5%</v>
+      </c>
+      <c r="K106" t="str">
+        <v>2.1%</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2026/08/26</v>
+      </c>
+      <c r="B107" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C107" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D107" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E107" t="str">
+        <v>2026/08/21</v>
+      </c>
+      <c r="F107" t="str">
+        <v>EIA 원유 재고 증감</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>4.405M</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026/08/26</v>
+      </c>
+      <c r="B108" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C108" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D108" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026/08/21</v>
+      </c>
+      <c r="F108" t="str">
+        <v>EIA 휘발유 재고 변동</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>0.688M</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B109" t="str">
+        <v>00:45</v>
+      </c>
+      <c r="C109" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D109" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>Fed Barkin 연설</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B110" t="str">
+        <v>02:00</v>
+      </c>
+      <c r="C110" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D110" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>국채 입찰(2년 FRN)</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v>0.050%</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B111" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C111" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D111" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B112" t="str">
+        <v>20:30</v>
+      </c>
+      <c r="C112" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="D112" t="str">
+        <v>유로 지역</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>ECB 통화 정책 회의</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B113" t="str">
+        <v>21:30</v>
+      </c>
+      <c r="C113" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D113" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026/08/22</v>
+      </c>
+      <c r="F113" t="str">
+        <v>신규 실업수당 청구건수</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v>209K</v>
+      </c>
+      <c r="J113" t="str">
+        <v>210.0K</v>
+      </c>
+      <c r="K113" t="str">
+        <v>206K</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B114" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C114" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D114" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G114">
+        <v>2</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B115" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C115" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="D115" t="str">
+        <v>유로 지역</v>
+      </c>
+      <c r="E115" t="str">
         <v>2026/08/31</v>
       </c>
-      <c r="B105" t="str">
+      <c r="F115" t="str">
+        <v>경제 심리지수</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v>97.5</v>
+      </c>
+      <c r="J115" t="str">
+        <v>97.7</v>
+      </c>
+      <c r="K115" t="str">
+        <v>96.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B116" t="str">
+        <v>22:45</v>
+      </c>
+      <c r="C116" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D116" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F116" t="str">
+        <v>시카고 PMI</v>
+      </c>
+      <c r="G116">
+        <v>2</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>57</v>
+      </c>
+      <c r="J116" t="str">
+        <v>56.1</v>
+      </c>
+      <c r="K116" t="str">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B117" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C117" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D117" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F117" t="str">
+        <v>미시간대 Consumer Sentiment(확정)</v>
+      </c>
+      <c r="G117">
+        <v>2</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>51.0</v>
+      </c>
+      <c r="J117" t="str">
+        <v>51.0</v>
+      </c>
+      <c r="K117" t="str">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026/08/29</v>
+      </c>
+      <c r="B118" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C118" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D118" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G118">
+        <v>2</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="B119" t="str">
         <v>23:30</v>
       </c>
-      <c r="C105" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D105" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E105" t="str">
+      <c r="C119" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D119" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E119" t="str">
         <v>2026/08/31</v>
       </c>
-      <c r="F105" t="str">
+      <c r="F119" t="str">
         <v>댈러스 연준 제조업지수</v>
       </c>
-      <c r="G105">
-        <v>2</v>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
-      <c r="J105" t="str">
-        <v/>
-      </c>
-      <c r="K105" t="str">
+      <c r="G119">
+        <v>2</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="K119" t="str">
         <v>1.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/incoming/경제지표.xlsx
+++ b/incoming/경제지표.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K107"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
   </cols>
@@ -439,77 +439,77 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026/08/03</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B2" t="str">
-        <v>22:45</v>
+        <v>18:00</v>
       </c>
       <c r="C2" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D2" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E2" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F2" t="str">
-        <v>S&amp;P 제조업 PMI(확정)</v>
+        <v>CPI상승률(속보) YoY</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" t="str">
-        <v>53.9</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>53.8</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>53.8</v>
+        <v>3.1%</v>
       </c>
       <c r="K2" t="str">
-        <v>53.8</v>
+        <v>2.9%</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026/08/03</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B3" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C3" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D3" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E3" t="str">
         <v>2026/07/31</v>
       </c>
       <c r="F3" t="str">
-        <v>ISM 제조업 PMI</v>
+        <v>실업률</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="str">
-        <v>55.6</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>54</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>53.7</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>53.3</v>
+        <v>6.3%</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026/08/03</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B4" t="str">
         <v>23:00</v>
@@ -521,33 +521,33 @@
         <v>미국</v>
       </c>
       <c r="E4" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F4" t="str">
-        <v>ISM 제조업 고용지수</v>
+        <v>ISM 제조업 PMI</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="str">
-        <v>52.8</v>
+        <v/>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>49.8</v>
+        <v>55</v>
       </c>
       <c r="K4" t="str">
-        <v>49.7</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B5" t="str">
-        <v>04:00</v>
+        <v>23:00</v>
       </c>
       <c r="C5" t="str">
         <v>USD</v>
@@ -556,10 +556,10 @@
         <v>미국</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>2026/08/31</v>
       </c>
       <c r="F5" t="str">
-        <v>미 재무부 차환발행 자금조달 추정지</v>
+        <v>ISM 제조업 고용지수</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>52.5</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>52.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B6" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C6" t="str">
         <v>USD</v>
@@ -591,33 +591,33 @@
         <v>미국</v>
       </c>
       <c r="E6" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F6" t="str">
-        <v>수입</v>
+        <v>JOLTs 구인 건수</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="str">
-        <v>$388.0B</v>
+        <v/>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>$ 385.0B</v>
+        <v>7.32M</v>
       </c>
       <c r="K6" t="str">
-        <v>$395.3B</v>
+        <v>7.359M</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/01</v>
       </c>
       <c r="B7" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C7" t="str">
         <v>USD</v>
@@ -626,33 +626,33 @@
         <v>미국</v>
       </c>
       <c r="E7" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F7" t="str">
-        <v>무역수지</v>
+        <v>RCM/TIPP 경제 낙관지수</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7" t="str">
-        <v>$-73.3B</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>$-73.0B</v>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <v>$ -73.0B</v>
+        <v>47</v>
       </c>
       <c r="K7" t="str">
-        <v>$-77.6B</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/02</v>
       </c>
       <c r="B8" t="str">
-        <v>21:30</v>
+        <v>05:30</v>
       </c>
       <c r="C8" t="str">
         <v>USD</v>
@@ -661,33 +661,33 @@
         <v>미국</v>
       </c>
       <c r="E8" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/28</v>
       </c>
       <c r="F8" t="str">
-        <v>수출</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v>$314.7B</v>
+        <v/>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>$312.0B</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>$317.6B</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/02</v>
       </c>
       <c r="B9" t="str">
-        <v>23:00</v>
+        <v>21:15</v>
       </c>
       <c r="C9" t="str">
         <v>USD</v>
@@ -699,27 +699,27 @@
         <v>2026/08/31</v>
       </c>
       <c r="F9" t="str">
-        <v>RCM/TIPP 경제 낙관지수</v>
+        <v>ADP 고용 증감</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>45.1</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>47.5</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>47</v>
+        <v>59.0K</v>
       </c>
       <c r="K9" t="str">
-        <v>45.5</v>
+        <v>44K</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/02</v>
       </c>
       <c r="B10" t="str">
         <v>23:00</v>
@@ -731,7 +731,7 @@
         <v>미국</v>
       </c>
       <c r="E10" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F10" t="str">
         <v>공장 주문 MoM</v>
@@ -740,24 +740,24 @@
         <v>2</v>
       </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>-0.1%</v>
+      </c>
+      <c r="K10" t="str">
         <v>-0.3%</v>
-      </c>
-      <c r="I10" t="str">
-        <v>0.2%</v>
-      </c>
-      <c r="J10" t="str">
-        <v>0.4%</v>
-      </c>
-      <c r="K10" t="str">
-        <v>-1.1%</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026/08/04</v>
+        <v>2026/09/02</v>
       </c>
       <c r="B11" t="str">
-        <v>23:00</v>
+        <v>23:30</v>
       </c>
       <c r="C11" t="str">
         <v>USD</v>
@@ -766,33 +766,33 @@
         <v>미국</v>
       </c>
       <c r="E11" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/28</v>
       </c>
       <c r="F11" t="str">
-        <v>JOLTs 구인 건수</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="str">
-        <v>7.359M</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>7.4M</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>7.3M</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>7.537M</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/02</v>
       </c>
       <c r="B12" t="str">
-        <v>05:30</v>
+        <v>23:30</v>
       </c>
       <c r="C12" t="str">
         <v>USD</v>
@@ -801,33 +801,33 @@
         <v>미국</v>
       </c>
       <c r="E12" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/28</v>
       </c>
       <c r="F12" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12" t="str">
-        <v>2.690M</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>-2M</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>3.296M</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B13" t="str">
-        <v>21:15</v>
+        <v>21:30</v>
       </c>
       <c r="C13" t="str">
         <v>USD</v>
@@ -836,30 +836,30 @@
         <v>미국</v>
       </c>
       <c r="E13" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/29</v>
       </c>
       <c r="F13" t="str">
-        <v>ADP 고용 증감</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13" t="str">
-        <v>44K</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>70K</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>90.0K</v>
+        <v>203.0K</v>
       </c>
       <c r="K13" t="str">
-        <v>95K</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B14" t="str">
         <v>21:30</v>
@@ -871,10 +871,10 @@
         <v>미국</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>2026/06/30</v>
       </c>
       <c r="F14" t="str">
-        <v>미 재무부 차환발행 발표</v>
+        <v>단위 노동 비용(확정) QoQ</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -889,15 +889,15 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>1.8%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B15" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C15" t="str">
         <v>USD</v>
@@ -909,30 +909,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F15" t="str">
-        <v>S&amp;P 서비스업 PMI(확정)</v>
+        <v>수입</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="str">
-        <v>54.6</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>53.6</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>53.6</v>
+        <v>$389.0B</v>
       </c>
       <c r="K15" t="str">
-        <v>51.2</v>
+        <v>$388.0B</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B16" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C16" t="str">
         <v>USD</v>
@@ -941,33 +941,33 @@
         <v>미국</v>
       </c>
       <c r="E16" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F16" t="str">
-        <v>S&amp;P 종합 PMI(확정)</v>
+        <v>비농업 생산성(확정) QoQ</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="str">
-        <v>54.5</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>53.6</v>
+        <v>1.4%</v>
       </c>
       <c r="J16" t="str">
-        <v>53.6</v>
+        <v>1.4%</v>
       </c>
       <c r="K16" t="str">
-        <v>51.9</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B17" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C17" t="str">
         <v>USD</v>
@@ -979,30 +979,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F17" t="str">
-        <v>ISM 서비스업 PMI</v>
+        <v>수출</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="str">
-        <v>54.1</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>54.5</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>54.5</v>
+        <v>$315.0B</v>
       </c>
       <c r="K17" t="str">
-        <v>54.0</v>
+        <v>$314.7B</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B18" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C18" t="str">
         <v>USD</v>
@@ -1014,30 +1014,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F18" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>무역수지</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="str">
-        <v>-1.643M</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>-1.3M</v>
+        <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>$-74.0B</v>
       </c>
       <c r="K18" t="str">
-        <v>0.007M</v>
+        <v>$-73.3B</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026/08/05</v>
+        <v>2026/09/03</v>
       </c>
       <c r="B19" t="str">
-        <v>23:30</v>
+        <v>23:00</v>
       </c>
       <c r="C19" t="str">
         <v>USD</v>
@@ -1046,45 +1046,45 @@
         <v>미국</v>
       </c>
       <c r="E19" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F19" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>ISM 서비스업 PMI</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="str">
-        <v>2.479M</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>-1.5M</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>53.8</v>
       </c>
       <c r="K19" t="str">
-        <v>-7.167M</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026/08/06</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B20" t="str">
-        <v>05:05</v>
+        <v>18:00</v>
       </c>
       <c r="C20" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D20" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F20" t="str">
-        <v>Fed Cook 연설</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1099,47 +1099,47 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026/08/06</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B21" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C21" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D21" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E21" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F21" t="str">
-        <v>소매판매 MoM</v>
+        <v>시간당 평균 소득 MoM</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" t="str">
-        <v>-0.3%</v>
+        <v/>
       </c>
       <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>0.2%</v>
+      </c>
+      <c r="K21" t="str">
         <v>0.1%</v>
-      </c>
-      <c r="J21" t="str">
-        <v>0.1%</v>
-      </c>
-      <c r="K21" t="str">
-        <v>0.4%</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026/08/06</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B22" t="str">
         <v>21:30</v>
@@ -1151,30 +1151,30 @@
         <v>미국</v>
       </c>
       <c r="E22" t="str">
-        <v>2026/08/01</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F22" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>비농업 고용자수</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="str">
-        <v>199K</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>202K</v>
+        <v/>
       </c>
       <c r="J22" t="str">
-        <v>199.0K</v>
+        <v>12.0K</v>
       </c>
       <c r="K22" t="str">
-        <v>198K</v>
+        <v>-23K</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026/08/06</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B23" t="str">
         <v>21:30</v>
@@ -1186,30 +1186,30 @@
         <v>미국</v>
       </c>
       <c r="E23" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F23" t="str">
-        <v>단위 노동 비용(잠정) QoQ</v>
+        <v>시간당 평균소득 YoY</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23" t="str">
-        <v>1.3%</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>2.1%</v>
+        <v/>
       </c>
       <c r="J23" t="str">
-        <v>2.0%</v>
+        <v>3.3%</v>
       </c>
       <c r="K23" t="str">
-        <v>1.3%</v>
+        <v>3.2%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026/08/06</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B24" t="str">
         <v>21:30</v>
@@ -1221,33 +1221,33 @@
         <v>미국</v>
       </c>
       <c r="E24" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F24" t="str">
-        <v>비농업 생산성(잠정) QoQ</v>
+        <v>실업률</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="str">
-        <v>1.4%</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>0.6%</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>0.6%</v>
+        <v>4.2%</v>
       </c>
       <c r="K24" t="str">
-        <v>0.8%</v>
+        <v>4.1%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/04</v>
       </c>
       <c r="B25" t="str">
-        <v>06:30</v>
+        <v>21:30</v>
       </c>
       <c r="C25" t="str">
         <v>USD</v>
@@ -1256,10 +1256,10 @@
         <v>미국</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>2026/08/31</v>
       </c>
       <c r="F25" t="str">
-        <v>Fed Musalem 연설</v>
+        <v>참가율</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1271,123 +1271,123 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>61.4%</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>61.4%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/07</v>
       </c>
       <c r="B26" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C26" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D26" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E26" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F26" t="str">
-        <v>참가율</v>
+        <v>GDP 성장률(3차 추정) YoY</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="str">
-        <v>61.4%</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>1%</v>
       </c>
       <c r="J26" t="str">
-        <v>61.6%</v>
+        <v>1.0%</v>
       </c>
       <c r="K26" t="str">
-        <v>61.5%</v>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/07</v>
       </c>
       <c r="B27" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C27" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D27" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E27" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F27" t="str">
-        <v>비농업 고용자수</v>
+        <v>고용 증감(확정) QoQ</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="str">
-        <v>-23K</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>80K</v>
+        <v/>
       </c>
       <c r="J27" t="str">
-        <v>79.0K</v>
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>20K</v>
+        <v>0.1%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/07</v>
       </c>
       <c r="B28" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C28" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D28" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E28" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F28" t="str">
-        <v>시간당 평균소득 YoY</v>
+        <v>GDP 성장률(3차 추정) QoQ</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28" t="str">
-        <v>3.2%</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>3.5%</v>
+        <v>0.4%</v>
       </c>
       <c r="J28" t="str">
-        <v>3.5%</v>
+        <v>0.4%</v>
       </c>
       <c r="K28" t="str">
-        <v>3.4%</v>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/08</v>
       </c>
       <c r="B29" t="str">
-        <v>21:30</v>
+        <v>21:15</v>
       </c>
       <c r="C29" t="str">
         <v>USD</v>
@@ -1396,33 +1396,33 @@
         <v>미국</v>
       </c>
       <c r="E29" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/22</v>
       </c>
       <c r="F29" t="str">
-        <v>실업률</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="str">
-        <v>4.1%</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>4.2%</v>
+        <v/>
       </c>
       <c r="J29" t="str">
-        <v>4.2%</v>
+        <v/>
       </c>
       <c r="K29" t="str">
-        <v>4.2%</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B30" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C30" t="str">
         <v>USD</v>
@@ -1431,33 +1431,33 @@
         <v>미국</v>
       </c>
       <c r="E30" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F30" t="str">
-        <v>시간당 평균 소득 MoM</v>
+        <v>국채 입찰(10Y Note)</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="J30" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026/08/07</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B31" t="str">
-        <v>23:00</v>
+        <v>05:30</v>
       </c>
       <c r="C31" t="str">
         <v>USD</v>
@@ -1466,10 +1466,10 @@
         <v>미국</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>2026/09/04</v>
       </c>
       <c r="F31" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1489,25 +1489,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026/08/09</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B32" t="str">
-        <v>01:45</v>
+        <v>21:15</v>
       </c>
       <c r="C32" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D32" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>2026/09/10</v>
       </c>
       <c r="F32" t="str">
-        <v>Fed Bowman 연설</v>
+        <v>ECB 금리결정</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1524,25 +1524,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026/08/11</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B33" t="str">
-        <v>04:00</v>
+        <v>21:15</v>
       </c>
       <c r="C33" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D33" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>2026/09/10</v>
       </c>
       <c r="F33" t="str">
-        <v>Fed Hammack 연설</v>
+        <v>예금 금리</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1554,15 +1554,15 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>2.25%</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026/08/11</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B34" t="str">
-        <v>21:15</v>
+        <v>21:30</v>
       </c>
       <c r="C34" t="str">
         <v>USD</v>
@@ -1571,16 +1571,16 @@
         <v>미국</v>
       </c>
       <c r="E34" t="str">
-        <v>2026/07/25</v>
+        <v>2026/09/05</v>
       </c>
       <c r="F34" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G34">
         <v>2</v>
       </c>
       <c r="H34" t="str">
-        <v>8.25K</v>
+        <v/>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1589,15 +1589,15 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>11.0K</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026/08/11</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B35" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C35" t="str">
         <v>USD</v>
@@ -1606,33 +1606,33 @@
         <v>미국</v>
       </c>
       <c r="E35" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F35" t="str">
-        <v>기존주택 판매</v>
+        <v>근원 PPI MoM</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35" t="str">
-        <v>4.06M</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>4.05M</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>4.06M</v>
+        <v/>
       </c>
       <c r="K35" t="str">
-        <v>4.13M</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026/08/11</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B36" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C36" t="str">
         <v>USD</v>
@@ -1641,68 +1641,68 @@
         <v>미국</v>
       </c>
       <c r="E36" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F36" t="str">
-        <v>기존주택 판매 MoM</v>
+        <v>PPI MoM</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" t="str">
-        <v>-1.7%</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>-0.7%</v>
+        <v/>
       </c>
       <c r="K36" t="str">
-        <v>-1.4%</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B37" t="str">
-        <v>05:30</v>
+        <v>21:45</v>
       </c>
       <c r="C37" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D37" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E37" t="str">
-        <v>2026/08/07</v>
+        <v/>
       </c>
       <c r="F37" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>ECB 기자 회견</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="str">
-        <v>9.072M</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>-0.50M</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>2.69M</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B38" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C38" t="str">
         <v>USD</v>
@@ -1711,33 +1711,33 @@
         <v>미국</v>
       </c>
       <c r="E38" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F38" t="str">
-        <v>소비자물가지수-계절조정</v>
+        <v>기존주택 판매</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38" t="str">
-        <v>332.81</v>
+        <v/>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>332.6</v>
+        <v/>
       </c>
       <c r="K38" t="str">
-        <v>332.57</v>
+        <v>4.06M</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/10</v>
       </c>
       <c r="B39" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C39" t="str">
         <v>USD</v>
@@ -1746,33 +1746,33 @@
         <v>미국</v>
       </c>
       <c r="E39" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F39" t="str">
-        <v>CPI상승률 YoY</v>
+        <v>기존주택 판매 MoM</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" t="str">
-        <v>3.4%</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v>3.4%</v>
+        <v/>
       </c>
       <c r="J39" t="str">
-        <v>3.4%</v>
+        <v/>
       </c>
       <c r="K39" t="str">
-        <v>3.5%</v>
+        <v>-1.7%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B40" t="str">
-        <v>21:30</v>
+        <v>01:00</v>
       </c>
       <c r="C40" t="str">
         <v>USD</v>
@@ -1781,33 +1781,33 @@
         <v>미국</v>
       </c>
       <c r="E40" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/04</v>
       </c>
       <c r="F40" t="str">
-        <v>근원 CPI상승률 MoM</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="K40" t="str">
-        <v>0%</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B41" t="str">
-        <v>21:30</v>
+        <v>01:00</v>
       </c>
       <c r="C41" t="str">
         <v>USD</v>
@@ -1816,33 +1816,33 @@
         <v>미국</v>
       </c>
       <c r="E41" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/04</v>
       </c>
       <c r="F41" t="str">
-        <v>근원 CPI상승률 YoY</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="str">
-        <v>2.5%</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>2.5%</v>
+        <v/>
       </c>
       <c r="J41" t="str">
-        <v>2.5%</v>
+        <v/>
       </c>
       <c r="K41" t="str">
-        <v>2.6%</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B42" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C42" t="str">
         <v>USD</v>
@@ -1851,30 +1851,30 @@
         <v>미국</v>
       </c>
       <c r="E42" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v>CPI상승률 MoM</v>
+        <v>국채 입찰(30Y Bond)</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>0.0%</v>
+        <v/>
       </c>
       <c r="K42" t="str">
-        <v>-0.4%</v>
+        <v>5.216%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B43" t="str">
         <v>21:30</v>
@@ -1886,33 +1886,33 @@
         <v>미국</v>
       </c>
       <c r="E43" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F43" t="str">
-        <v>소비자물가지수</v>
+        <v>근원 CPI상승률 MoM</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="str">
-        <v>333.92</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>333.99</v>
+        <v/>
       </c>
       <c r="J43" t="str">
-        <v>334.03</v>
+        <v>0.2%</v>
       </c>
       <c r="K43" t="str">
-        <v>333.95</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B44" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -1921,33 +1921,33 @@
         <v>미국</v>
       </c>
       <c r="E44" t="str">
-        <v>2026/08/07</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F44" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>CPI상승률 YoY</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="str">
-        <v>-0.968M</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>-1.2M</v>
+        <v/>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>-1.643M</v>
+        <v>3.4%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026/08/12</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B45" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -1956,33 +1956,33 @@
         <v>미국</v>
       </c>
       <c r="E45" t="str">
-        <v>2026/08/07</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F45" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>CPI상승률 MoM</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" t="str">
-        <v>17.422M</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>-1.4M</v>
+        <v/>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>2.479M</v>
+        <v>0.1%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B46" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -1991,16 +1991,16 @@
         <v>미국</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>2026/08/31</v>
       </c>
       <c r="F46" t="str">
-        <v>국채 입찰(10Y Note)</v>
+        <v>근원 CPI상승률 YoY</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="str">
-        <v>4.683%</v>
+        <v/>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2009,15 +2009,15 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>4.580%</v>
+        <v>2.5%</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B47" t="str">
-        <v>03:00</v>
+        <v>21:30</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -2026,68 +2026,68 @@
         <v>미국</v>
       </c>
       <c r="E47" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F47" t="str">
-        <v>월간 예산 성명서</v>
+        <v>소비자물가지수</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47" t="str">
-        <v>$-432B</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v>$-346B</v>
+        <v/>
       </c>
       <c r="J47" t="str">
-        <v>$-340.0B</v>
+        <v/>
       </c>
       <c r="K47" t="str">
-        <v>$-120B</v>
+        <v>333.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B48" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C48" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D48" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E48" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F48" t="str">
-        <v>산업생산 MoM</v>
+        <v>소비자물가지수-계절조정</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48" t="str">
-        <v>0%</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v>-0.1%</v>
+        <v/>
       </c>
       <c r="J48" t="str">
-        <v>-0.1%</v>
+        <v/>
       </c>
       <c r="K48" t="str">
-        <v>0.3%</v>
+        <v>332.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/11</v>
       </c>
       <c r="B49" t="str">
-        <v>21:15</v>
+        <v>23:00</v>
       </c>
       <c r="C49" t="str">
         <v>USD</v>
@@ -2096,10 +2096,10 @@
         <v>미국</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>2026/09/30</v>
       </c>
       <c r="F49" t="str">
-        <v>Fed Hammack 연설</v>
+        <v>미시간대 Consumer Sentiment(잠정)</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/12</v>
       </c>
       <c r="B50" t="str">
-        <v>21:30</v>
+        <v>03:00</v>
       </c>
       <c r="C50" t="str">
         <v>USD</v>
@@ -2131,103 +2131,103 @@
         <v>미국</v>
       </c>
       <c r="E50" t="str">
-        <v>2026/08/08</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F50" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>월간 예산 성명서</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50" t="str">
-        <v>209K</v>
+        <v/>
       </c>
       <c r="I50" t="str">
-        <v>202K</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v>204.0K</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>200K</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/15</v>
       </c>
       <c r="B51" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C51" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D51" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E51" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F51" t="str">
-        <v>근원 PPI MoM</v>
+        <v>ZEW 경제심리지수</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="J51" t="str">
-        <v>0.2%</v>
+        <v>5</v>
       </c>
       <c r="K51" t="str">
-        <v>0.4%</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/15</v>
       </c>
       <c r="B52" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C52" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D52" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E52" t="str">
         <v>2026/07/31</v>
       </c>
       <c r="F52" t="str">
-        <v>PPI MoM</v>
+        <v>무역수지</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" t="str">
-        <v>0%</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="J52" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="K52" t="str">
-        <v>-0.1%</v>
+        <v>€8.6B</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026/08/13</v>
+        <v>2026/09/15</v>
       </c>
       <c r="B53" t="str">
-        <v>21:40</v>
+        <v>21:15</v>
       </c>
       <c r="C53" t="str">
         <v>USD</v>
@@ -2236,10 +2236,10 @@
         <v>미국</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>2026/08/29</v>
       </c>
       <c r="F53" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/15</v>
       </c>
       <c r="B54" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C54" t="str">
         <v>USD</v>
@@ -2271,65 +2271,65 @@
         <v>미국</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>2026/09/30</v>
       </c>
       <c r="F54" t="str">
-        <v>국채 입찰(30Y Bond)</v>
+        <v>뉴욕 엠파이어스테이트 제조업지수</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="str">
-        <v>5.216%</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>-9</v>
       </c>
       <c r="K54" t="str">
-        <v>5.058%</v>
+        <v>20.60</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B55" t="str">
-        <v>18:00</v>
+        <v>05:30</v>
       </c>
       <c r="C55" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D55" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E55" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/11</v>
       </c>
       <c r="F55" t="str">
-        <v>GDP 성장률(2차 추정) QoQ</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G55">
         <v>2</v>
       </c>
       <c r="H55" t="str">
-        <v>0.4%</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v>0.4%</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>0.4%</v>
+        <v/>
       </c>
       <c r="K55" t="str">
-        <v>0.0%</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B56" t="str">
         <v>18:00</v>
@@ -2341,100 +2341,100 @@
         <v>유로 지역</v>
       </c>
       <c r="E56" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F56" t="str">
-        <v>고용 증감(잠정) QoQ</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
       <c r="H56" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="I56" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J56" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="K56" t="str">
-        <v>0.1%</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B57" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C57" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D57" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E57" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F57" t="str">
-        <v>GDP 성장률(2차 추정) YoY</v>
+        <v>수입가격 MoM</v>
       </c>
       <c r="G57">
         <v>2</v>
       </c>
       <c r="H57" t="str">
-        <v>1%</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v>1%</v>
+        <v/>
       </c>
       <c r="J57" t="str">
-        <v>1.0%</v>
+        <v/>
       </c>
       <c r="K57" t="str">
-        <v>0.5%</v>
+        <v>-0.4%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B58" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C58" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D58" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E58" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F58" t="str">
-        <v>무역수지</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" t="str">
-        <v>€8.6B</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v>€-2.2B</v>
+        <v/>
       </c>
       <c r="J58" t="str">
-        <v>€ 5B</v>
+        <v/>
       </c>
       <c r="K58" t="str">
-        <v>€-9B</v>
+        <v>-0.6%</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B59" t="str">
         <v>21:30</v>
@@ -2446,30 +2446,30 @@
         <v>미국</v>
       </c>
       <c r="E59" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F59" t="str">
-        <v>소매판매 MoM</v>
+        <v>수출가격 MoM</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" t="str">
-        <v>-0.6%</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J59" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="K59" t="str">
-        <v>0.2%</v>
+        <v>-1.3%</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B60" t="str">
         <v>23:00</v>
@@ -2481,30 +2481,30 @@
         <v>미국</v>
       </c>
       <c r="E60" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F60" t="str">
-        <v>미시간대 Consumer Sentiment(잠정)</v>
+        <v>기업 재고 MoM</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60" t="str">
-        <v>51.0</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v>54.5</v>
+        <v/>
       </c>
       <c r="J60" t="str">
-        <v>54.6</v>
+        <v/>
       </c>
       <c r="K60" t="str">
-        <v>55.2</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B61" t="str">
         <v>23:00</v>
@@ -2516,33 +2516,33 @@
         <v>미국</v>
       </c>
       <c r="E61" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F61" t="str">
-        <v>기업 재고 MoM</v>
+        <v>NAHB 주택 시장지수</v>
       </c>
       <c r="G61">
         <v>2</v>
       </c>
       <c r="H61" t="str">
-        <v>0%</v>
+        <v/>
       </c>
       <c r="I61" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>0.2%</v>
+        <v>42</v>
       </c>
       <c r="K61" t="str">
-        <v>0.4%</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026/08/17</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B62" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C62" t="str">
         <v>USD</v>
@@ -2551,33 +2551,33 @@
         <v>미국</v>
       </c>
       <c r="E62" t="str">
-        <v>2026/08/31</v>
+        <v>2026/09/11</v>
       </c>
       <c r="F62" t="str">
-        <v>뉴욕 엠파이어스테이트 제조업지수</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62" t="str">
-        <v>20.60</v>
+        <v/>
       </c>
       <c r="I62" t="str">
-        <v>11</v>
+        <v/>
       </c>
       <c r="J62" t="str">
-        <v>12</v>
+        <v/>
       </c>
       <c r="K62" t="str">
-        <v>15.60</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026/08/17</v>
+        <v>2026/09/16</v>
       </c>
       <c r="B63" t="str">
-        <v>23:00</v>
+        <v>23:30</v>
       </c>
       <c r="C63" t="str">
         <v>USD</v>
@@ -2586,33 +2586,33 @@
         <v>미국</v>
       </c>
       <c r="E63" t="str">
-        <v>2026/08/31</v>
+        <v>2026/09/11</v>
       </c>
       <c r="F63" t="str">
-        <v>NAHB 주택 시장지수</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G63">
         <v>2</v>
       </c>
       <c r="H63" t="str">
-        <v>35</v>
+        <v/>
       </c>
       <c r="I63" t="str">
-        <v>33</v>
+        <v/>
       </c>
       <c r="J63" t="str">
-        <v>34</v>
+        <v/>
       </c>
       <c r="K63" t="str">
-        <v>34</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B64" t="str">
-        <v>05:00</v>
+        <v>03:00</v>
       </c>
       <c r="C64" t="str">
         <v>USD</v>
@@ -2621,68 +2621,68 @@
         <v>미국</v>
       </c>
       <c r="E64" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/16</v>
       </c>
       <c r="F64" t="str">
-        <v>장기 TIC 순 유출입</v>
+        <v>FED 금리결정(상단)</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" t="str">
-        <v>$172.7B</v>
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v>$151.4B</v>
+        <v/>
       </c>
       <c r="J64" t="str">
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>$231.2B</v>
+        <v>3.75%</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B65" t="str">
-        <v>18:00</v>
+        <v>03:30</v>
       </c>
       <c r="C65" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D65" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E65" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F65" t="str">
-        <v>ZEW 경제심리지수</v>
+        <v>Fed 기자 회견</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" t="str">
-        <v>31.4</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>25.4</v>
+        <v/>
       </c>
       <c r="J65" t="str">
-        <v>24</v>
+        <v/>
       </c>
       <c r="K65" t="str">
-        <v>23.4</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B66" t="str">
-        <v>21:15</v>
+        <v>05:00</v>
       </c>
       <c r="C66" t="str">
         <v>USD</v>
@@ -2691,16 +2691,16 @@
         <v>미국</v>
       </c>
       <c r="E66" t="str">
-        <v>2026/08/01</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F66" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>장기 TIC 순 유출입</v>
       </c>
       <c r="G66">
         <v>2</v>
       </c>
       <c r="H66" t="str">
-        <v>9.5K</v>
+        <v/>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2709,47 +2709,47 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>8.25K</v>
+        <v>$172.7B</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B67" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C67" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D67" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E67" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F67" t="str">
-        <v>주택 착공 MoM</v>
+        <v>CPI상승률(확정) YoY</v>
       </c>
       <c r="G67">
         <v>2</v>
       </c>
       <c r="H67" t="str">
-        <v>-12.4%</v>
+        <v/>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v>-4.7%</v>
+        <v/>
       </c>
       <c r="K67" t="str">
-        <v>19.7%</v>
+        <v>2.9%</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B68" t="str">
         <v>21:30</v>
@@ -2761,30 +2761,30 @@
         <v>미국</v>
       </c>
       <c r="E68" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/12</v>
       </c>
       <c r="F68" t="str">
-        <v>주택 착공</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="str">
-        <v>1.239M</v>
+        <v/>
       </c>
       <c r="I68" t="str">
-        <v>1.35M</v>
+        <v/>
       </c>
       <c r="J68" t="str">
-        <v>1.36M</v>
+        <v/>
       </c>
       <c r="K68" t="str">
-        <v>1.415M</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B69" t="str">
         <v>21:30</v>
@@ -2796,30 +2796,30 @@
         <v>미국</v>
       </c>
       <c r="E69" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F69" t="str">
-        <v>수입가격 MoM</v>
+        <v>필라델피아 연준 제조업지수</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="str">
-        <v>-0.4%</v>
+        <v/>
       </c>
       <c r="I69" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J69" t="str">
-        <v>0.2%</v>
+        <v>7</v>
       </c>
       <c r="K69" t="str">
-        <v>-0.3%</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B70" t="str">
         <v>21:30</v>
@@ -2831,33 +2831,33 @@
         <v>미국</v>
       </c>
       <c r="E70" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F70" t="str">
-        <v>수출가격 MoM</v>
+        <v>주택 착공</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="str">
-        <v>-1.3%</v>
+        <v/>
       </c>
       <c r="I70" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="J70" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="K70" t="str">
-        <v>-0.7%</v>
+        <v>1.239M</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B71" t="str">
-        <v>22:15</v>
+        <v>21:30</v>
       </c>
       <c r="C71" t="str">
         <v>USD</v>
@@ -2866,30 +2866,30 @@
         <v>미국</v>
       </c>
       <c r="E71" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F71" t="str">
-        <v>산업생산 MoM</v>
+        <v>주택 착공 MoM</v>
       </c>
       <c r="G71">
         <v>2</v>
       </c>
       <c r="H71" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="J71" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="K71" t="str">
-        <v>0.3%</v>
+        <v>-12.4%</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B72" t="str">
         <v>23:00</v>
@@ -2901,7 +2901,7 @@
         <v>미국</v>
       </c>
       <c r="E72" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F72" t="str">
         <v>잠정 주택 판매 MoM</v>
@@ -2910,21 +2910,21 @@
         <v>2</v>
       </c>
       <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
         <v>-2.3%</v>
-      </c>
-      <c r="I72" t="str">
-        <v>0.3%</v>
-      </c>
-      <c r="J72" t="str">
-        <v>0.9%</v>
-      </c>
-      <c r="K72" t="str">
-        <v>-4.8%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026/08/18</v>
+        <v>2026/09/17</v>
       </c>
       <c r="B73" t="str">
         <v>23:00</v>
@@ -2936,7 +2936,7 @@
         <v>미국</v>
       </c>
       <c r="E73" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F73" t="str">
         <v>잠정주택 판매 YoY</v>
@@ -2945,24 +2945,24 @@
         <v>2</v>
       </c>
       <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
         <v>-2.2%</v>
-      </c>
-      <c r="I73" t="str">
-        <v/>
-      </c>
-      <c r="J73" t="str">
-        <v>1.4%</v>
-      </c>
-      <c r="K73" t="str">
-        <v>-0.3%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026/08/19</v>
+        <v>2026/09/18</v>
       </c>
       <c r="B74" t="str">
-        <v>06:00</v>
+        <v>22:15</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -2971,16 +2971,16 @@
         <v>미국</v>
       </c>
       <c r="E74" t="str">
-        <v>2026/08/14</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F74" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74" t="str">
-        <v>-3.28M</v>
+        <v/>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2989,27 +2989,27 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>9.072M</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026/08/19</v>
+        <v>2026/09/21</v>
       </c>
       <c r="B75" t="str">
-        <v>16:10</v>
+        <v>21:30</v>
       </c>
       <c r="C75" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D75" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>2026/08/31</v>
       </c>
       <c r="F75" t="str">
-        <v>ECB 총재 Lagarde 연설</v>
+        <v>시카고 연준 국가 활동지수</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -3029,45 +3029,45 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026/08/19</v>
+        <v>2026/09/22</v>
       </c>
       <c r="B76" t="str">
-        <v>18:00</v>
+        <v>21:15</v>
       </c>
       <c r="C76" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D76" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E76" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/05</v>
       </c>
       <c r="F76" t="str">
-        <v>CPI상승률(확정) YoY</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76" t="str">
-        <v>2.9%</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v>2.9%</v>
+        <v/>
       </c>
       <c r="J76" t="str">
-        <v>2.9%</v>
+        <v/>
       </c>
       <c r="K76" t="str">
-        <v>2.8%</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026/08/19</v>
+        <v>2026/09/23</v>
       </c>
       <c r="B77" t="str">
-        <v>23:30</v>
+        <v>05:30</v>
       </c>
       <c r="C77" t="str">
         <v>USD</v>
@@ -3076,30 +3076,30 @@
         <v>미국</v>
       </c>
       <c r="E77" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/18</v>
       </c>
       <c r="F77" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77" t="str">
-        <v>4.405M</v>
+        <v/>
       </c>
       <c r="I77" t="str">
-        <v>-0.6M</v>
+        <v/>
       </c>
       <c r="J77" t="str">
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>17.422M</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026/08/19</v>
+        <v>2026/09/23</v>
       </c>
       <c r="B78" t="str">
         <v>23:30</v>
@@ -3111,33 +3111,33 @@
         <v>미국</v>
       </c>
       <c r="E78" t="str">
-        <v>2026/08/14</v>
+        <v>2026/09/18</v>
       </c>
       <c r="F78" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78" t="str">
-        <v>0.688M</v>
+        <v/>
       </c>
       <c r="I78" t="str">
-        <v>-1.2M</v>
+        <v/>
       </c>
       <c r="J78" t="str">
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>-0.968M</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026/08/20</v>
+        <v>2026/09/23</v>
       </c>
       <c r="B79" t="str">
-        <v>03:00</v>
+        <v>23:30</v>
       </c>
       <c r="C79" t="str">
         <v>USD</v>
@@ -3146,13 +3146,13 @@
         <v>미국</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>2026/09/18</v>
       </c>
       <c r="F79" t="str">
-        <v>FOMC 회의록</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026/08/20</v>
+        <v>2026/09/24</v>
       </c>
       <c r="B80" t="str">
-        <v>20:30</v>
+        <v>02:00</v>
       </c>
       <c r="C80" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D80" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>ECB 통화 정책 회의</v>
+        <v>국채 입찰(2년 FRN)</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026/08/20</v>
+        <v>2026/09/24</v>
       </c>
       <c r="B81" t="str">
         <v>21:30</v>
@@ -3216,7 +3216,7 @@
         <v>미국</v>
       </c>
       <c r="E81" t="str">
-        <v>2026/08/15</v>
+        <v>2026/09/19</v>
       </c>
       <c r="F81" t="str">
         <v>신규 실업수당 청구건수</v>
@@ -3225,21 +3225,21 @@
         <v>2</v>
       </c>
       <c r="H81" t="str">
-        <v>206K</v>
+        <v/>
       </c>
       <c r="I81" t="str">
-        <v>210K</v>
+        <v/>
       </c>
       <c r="J81" t="str">
-        <v>201.0K</v>
+        <v/>
       </c>
       <c r="K81" t="str">
-        <v>212K</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026/08/20</v>
+        <v>2026/09/24</v>
       </c>
       <c r="B82" t="str">
         <v>21:30</v>
@@ -3251,68 +3251,68 @@
         <v>미국</v>
       </c>
       <c r="E82" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F82" t="str">
-        <v>필라델피아 연준 제조업지수</v>
+        <v>경상수지</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82" t="str">
-        <v>47.4</v>
+        <v/>
       </c>
       <c r="I82" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="J82" t="str">
-        <v>25</v>
+        <v>$ -220B</v>
       </c>
       <c r="K82" t="str">
-        <v>41.4</v>
+        <v>$-226.8B</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/24</v>
       </c>
       <c r="B83" t="str">
-        <v>18:00</v>
+        <v>23:00</v>
       </c>
       <c r="C83" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D83" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E83" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F83" t="str">
-        <v>협상 임금 인상률</v>
+        <v>신규주택 판매</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83" t="str">
-        <v>2.44%</v>
+        <v/>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v>2.5%</v>
+        <v/>
       </c>
       <c r="K83" t="str">
-        <v>2.56%</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/24</v>
       </c>
       <c r="B84" t="str">
-        <v>22:45</v>
+        <v>23:00</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -3324,30 +3324,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F84" t="str">
-        <v>S&amp;P 서비스업 PMI(속보)</v>
+        <v>신규주택 판매 MoM</v>
       </c>
       <c r="G84">
         <v>2</v>
       </c>
       <c r="H84" t="str">
-        <v>56.8</v>
+        <v/>
       </c>
       <c r="I84" t="str">
-        <v>54</v>
+        <v/>
       </c>
       <c r="J84" t="str">
-        <v>53.8</v>
+        <v/>
       </c>
       <c r="K84" t="str">
-        <v>54.6</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/25</v>
       </c>
       <c r="B85" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -3359,30 +3359,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F85" t="str">
-        <v>S&amp;P 제조업 PMI(속보)</v>
+        <v>내구재 주문 MoM</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" t="str">
-        <v>53.2</v>
+        <v/>
       </c>
       <c r="I85" t="str">
-        <v>53.9</v>
+        <v/>
       </c>
       <c r="J85" t="str">
-        <v>53.5</v>
+        <v/>
       </c>
       <c r="K85" t="str">
-        <v>53.9</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/25</v>
       </c>
       <c r="B86" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C86" t="str">
         <v>USD</v>
@@ -3394,30 +3394,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F86" t="str">
-        <v>S&amp;P 종합 PMI(속보)</v>
+        <v>내구재 주문(운송 제외) MoM</v>
       </c>
       <c r="G86">
         <v>2</v>
       </c>
       <c r="H86" t="str">
-        <v>56.0</v>
+        <v/>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v>53.2</v>
+        <v/>
       </c>
       <c r="K86" t="str">
-        <v>54.5</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026/08/24</v>
+        <v>2026/09/25</v>
       </c>
       <c r="B87" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C87" t="str">
         <v>USD</v>
@@ -3426,10 +3426,10 @@
         <v>미국</v>
       </c>
       <c r="E87" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F87" t="str">
-        <v>시카고 연준 국가 활동지수</v>
+        <v>미시간대 Consumer Sentiment(확정)</v>
       </c>
       <c r="G87">
         <v>2</v>
@@ -3441,18 +3441,18 @@
         <v/>
       </c>
       <c r="J87" t="str">
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="K87" t="str">
-        <v>-0.02</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/28</v>
       </c>
       <c r="B88" t="str">
-        <v>21:00</v>
+        <v>23:30</v>
       </c>
       <c r="C88" t="str">
         <v>USD</v>
@@ -3461,10 +3461,10 @@
         <v>미국</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>2026/09/30</v>
       </c>
       <c r="F88" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>댈러스 연준 제조업지수</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -3484,22 +3484,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B89" t="str">
-        <v>21:15</v>
+        <v>18:00</v>
       </c>
       <c r="C89" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D89" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E89" t="str">
-        <v>2026/08/08</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F89" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>경제 심리지수</v>
       </c>
       <c r="G89">
         <v>2</v>
@@ -3511,18 +3511,18 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>94.5</v>
       </c>
       <c r="K89" t="str">
-        <v>9.5K</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B90" t="str">
-        <v>22:00</v>
+        <v>21:15</v>
       </c>
       <c r="C90" t="str">
         <v>USD</v>
@@ -3531,10 +3531,10 @@
         <v>미국</v>
       </c>
       <c r="E90" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/12</v>
       </c>
       <c r="F90" t="str">
-        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -3543,18 +3543,18 @@
         <v/>
       </c>
       <c r="I90" t="str">
-        <v>1.7%</v>
+        <v/>
       </c>
       <c r="J90" t="str">
-        <v>1.8%</v>
+        <v/>
       </c>
       <c r="K90" t="str">
-        <v>1.6%</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B91" t="str">
         <v>22:00</v>
@@ -3566,7 +3566,7 @@
         <v>미국</v>
       </c>
       <c r="E91" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F91" t="str">
         <v>S&amp;P/Case-Shiller 주택가격 MoM</v>
@@ -3581,18 +3581,18 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v>0.4%</v>
+        <v/>
       </c>
       <c r="K91" t="str">
-        <v>0.9%</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B92" t="str">
-        <v>23:00</v>
+        <v>22:00</v>
       </c>
       <c r="C92" t="str">
         <v>USD</v>
@@ -3604,7 +3604,7 @@
         <v>2026/07/31</v>
       </c>
       <c r="F92" t="str">
-        <v>신규주택 판매</v>
+        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
       </c>
       <c r="G92">
         <v>2</v>
@@ -3613,18 +3613,18 @@
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>0.62M</v>
+        <v/>
       </c>
       <c r="J92" t="str">
-        <v>0.62M</v>
+        <v/>
       </c>
       <c r="K92" t="str">
-        <v>0.628M</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B93" t="str">
         <v>23:00</v>
@@ -3636,13 +3636,13 @@
         <v>미국</v>
       </c>
       <c r="E93" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F93" t="str">
-        <v>신규주택 판매 MoM</v>
+        <v>JOLTs 구인 건수</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -3651,15 +3651,15 @@
         <v/>
       </c>
       <c r="J93" t="str">
-        <v>-1.3%</v>
+        <v/>
       </c>
       <c r="K93" t="str">
-        <v>1.6%</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026/08/25</v>
+        <v>2026/09/29</v>
       </c>
       <c r="B94" t="str">
         <v>23:00</v>
@@ -3671,7 +3671,7 @@
         <v>미국</v>
       </c>
       <c r="E94" t="str">
-        <v>2026/08/31</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F94" t="str">
         <v>CB 소비자 신뢰지수</v>
@@ -3683,21 +3683,21 @@
         <v/>
       </c>
       <c r="I94" t="str">
-        <v>91.2</v>
+        <v/>
       </c>
       <c r="J94" t="str">
-        <v>90.9</v>
+        <v/>
       </c>
       <c r="K94" t="str">
-        <v>90.8</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B95" t="str">
-        <v>05:00</v>
+        <v>05:30</v>
       </c>
       <c r="C95" t="str">
         <v>USD</v>
@@ -3706,10 +3706,10 @@
         <v>미국</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>2026/09/25</v>
       </c>
       <c r="F95" t="str">
-        <v>Fed Barkin 연설</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G95">
         <v>2</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B96" t="str">
-        <v>05:30</v>
+        <v>21:15</v>
       </c>
       <c r="C96" t="str">
         <v>USD</v>
@@ -3741,10 +3741,10 @@
         <v>미국</v>
       </c>
       <c r="E96" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F96" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>ADP 고용 증감</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -3756,15 +3756,15 @@
         <v/>
       </c>
       <c r="J96" t="str">
-        <v/>
+        <v>75K</v>
       </c>
       <c r="K96" t="str">
-        <v>-3.28M</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B97" t="str">
         <v>21:30</v>
@@ -3776,30 +3776,30 @@
         <v>미국</v>
       </c>
       <c r="E97" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F97" t="str">
-        <v>개인 지출 MoM</v>
+        <v>PCE 물가지수 MoM</v>
       </c>
       <c r="G97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" t="str">
         <v/>
       </c>
       <c r="I97" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="J97" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="K97" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B98" t="str">
         <v>21:30</v>
@@ -3811,13 +3811,13 @@
         <v>미국</v>
       </c>
       <c r="E98" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F98" t="str">
-        <v>기업 이익(잠정) QoQ</v>
+        <v>근원 PCE 물가지수 MoM</v>
       </c>
       <c r="G98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -3826,15 +3826,15 @@
         <v/>
       </c>
       <c r="J98" t="str">
-        <v>0.7%</v>
+        <v/>
       </c>
       <c r="K98" t="str">
-        <v>0.5%</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B99" t="str">
         <v>21:30</v>
@@ -3846,10 +3846,10 @@
         <v>미국</v>
       </c>
       <c r="E99" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F99" t="str">
-        <v>개인 소득 MoM</v>
+        <v>GDP성장률(3차 예측) QoQ</v>
       </c>
       <c r="G99">
         <v>3</v>
@@ -3858,18 +3858,18 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="J99" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="K99" t="str">
-        <v>0.2%</v>
+        <v>2.1%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B100" t="str">
         <v>21:30</v>
@@ -3881,10 +3881,10 @@
         <v>미국</v>
       </c>
       <c r="E100" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F100" t="str">
-        <v>PCE 물가지수 MoM</v>
+        <v>기업 이익(확정) QoQ</v>
       </c>
       <c r="G100">
         <v>2</v>
@@ -3893,18 +3893,18 @@
         <v/>
       </c>
       <c r="I100" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
       <c r="J100" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="K100" t="str">
-        <v>-0.1%</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B101" t="str">
         <v>21:30</v>
@@ -3916,10 +3916,10 @@
         <v>미국</v>
       </c>
       <c r="E101" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F101" t="str">
-        <v>내구재 주문(운송 제외) MoM</v>
+        <v>PCE 물가지수 YoY</v>
       </c>
       <c r="G101">
         <v>2</v>
@@ -3928,18 +3928,18 @@
         <v/>
       </c>
       <c r="I101" t="str">
-        <v>0.5%</v>
+        <v/>
       </c>
       <c r="J101" t="str">
-        <v>0.3%</v>
+        <v/>
       </c>
       <c r="K101" t="str">
-        <v>0.6%</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B102" t="str">
         <v>21:30</v>
@@ -3951,30 +3951,30 @@
         <v>미국</v>
       </c>
       <c r="E102" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F102" t="str">
-        <v>내구재 주문 MoM</v>
+        <v>GDP 물가지수(3차 예측) QoQ</v>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H102" t="str">
         <v/>
       </c>
       <c r="I102" t="str">
-        <v>0.7%</v>
+        <v/>
       </c>
       <c r="J102" t="str">
-        <v>0.5%</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>0.3%</v>
+        <v>3.6%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B103" t="str">
         <v>21:30</v>
@@ -3986,30 +3986,30 @@
         <v>미국</v>
       </c>
       <c r="E103" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F103" t="str">
-        <v>GDP 물가지수(2차 예측) QoQ</v>
+        <v>개인 지출 MoM</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H103" t="str">
         <v/>
       </c>
       <c r="I103" t="str">
-        <v>6.3%</v>
+        <v/>
       </c>
       <c r="J103" t="str">
-        <v>6.3%</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>3.6%</v>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B104" t="str">
         <v>21:30</v>
@@ -4021,13 +4021,13 @@
         <v>미국</v>
       </c>
       <c r="E104" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F104" t="str">
-        <v>PCE 물가지수 YoY</v>
+        <v>개인 소득 MoM</v>
       </c>
       <c r="G104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H104" t="str">
         <v/>
@@ -4036,18 +4036,18 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>3.7%</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>3.7%</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B105" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C105" t="str">
         <v>USD</v>
@@ -4056,33 +4056,33 @@
         <v>미국</v>
       </c>
       <c r="E105" t="str">
-        <v>2026/07/31</v>
+        <v>2026/09/30</v>
       </c>
       <c r="F105" t="str">
-        <v>근원 PCE 물가지수 MoM</v>
+        <v>시카고 PMI</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H105" t="str">
         <v/>
       </c>
       <c r="I105" t="str">
-        <v>0.2%</v>
+        <v/>
       </c>
       <c r="J105" t="str">
-        <v>0.3%</v>
+        <v>55.9</v>
       </c>
       <c r="K105" t="str">
-        <v>0.1%</v>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B106" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C106" t="str">
         <v>USD</v>
@@ -4091,30 +4091,30 @@
         <v>미국</v>
       </c>
       <c r="E106" t="str">
-        <v>2026/06/30</v>
+        <v>2026/09/25</v>
       </c>
       <c r="F106" t="str">
-        <v>GDP성장률(2차 예측) QoQ</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106" t="str">
         <v/>
       </c>
       <c r="I106" t="str">
-        <v>1.5%</v>
+        <v/>
       </c>
       <c r="J106" t="str">
-        <v>1.5%</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>2.1%</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026/08/26</v>
+        <v>2026/09/30</v>
       </c>
       <c r="B107" t="str">
         <v>23:30</v>
@@ -4126,10 +4126,10 @@
         <v>미국</v>
       </c>
       <c r="E107" t="str">
-        <v>2026/08/21</v>
+        <v>2026/09/25</v>
       </c>
       <c r="F107" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -4144,432 +4144,12 @@
         <v/>
       </c>
       <c r="K107" t="str">
-        <v>4.405M</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>2026/08/26</v>
-      </c>
-      <c r="B108" t="str">
-        <v>23:30</v>
-      </c>
-      <c r="C108" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D108" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E108" t="str">
-        <v>2026/08/21</v>
-      </c>
-      <c r="F108" t="str">
-        <v>EIA 휘발유 재고 변동</v>
-      </c>
-      <c r="G108">
-        <v>2</v>
-      </c>
-      <c r="H108" t="str">
-        <v/>
-      </c>
-      <c r="I108" t="str">
-        <v/>
-      </c>
-      <c r="J108" t="str">
-        <v/>
-      </c>
-      <c r="K108" t="str">
-        <v>0.688M</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>2026/08/27</v>
-      </c>
-      <c r="B109" t="str">
-        <v>00:45</v>
-      </c>
-      <c r="C109" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D109" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E109" t="str">
-        <v/>
-      </c>
-      <c r="F109" t="str">
-        <v>Fed Barkin 연설</v>
-      </c>
-      <c r="G109">
-        <v>2</v>
-      </c>
-      <c r="H109" t="str">
-        <v/>
-      </c>
-      <c r="I109" t="str">
-        <v/>
-      </c>
-      <c r="J109" t="str">
-        <v/>
-      </c>
-      <c r="K109" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>2026/08/27</v>
-      </c>
-      <c r="B110" t="str">
-        <v>02:00</v>
-      </c>
-      <c r="C110" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D110" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E110" t="str">
-        <v/>
-      </c>
-      <c r="F110" t="str">
-        <v>국채 입찰(2년 FRN)</v>
-      </c>
-      <c r="G110">
-        <v>2</v>
-      </c>
-      <c r="H110" t="str">
-        <v/>
-      </c>
-      <c r="I110" t="str">
-        <v/>
-      </c>
-      <c r="J110" t="str">
-        <v/>
-      </c>
-      <c r="K110" t="str">
-        <v>0.050%</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>2026/08/27</v>
-      </c>
-      <c r="B111" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="C111" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D111" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E111" t="str">
-        <v/>
-      </c>
-      <c r="F111" t="str">
-        <v>Jackson Hole 심포지엄</v>
-      </c>
-      <c r="G111">
-        <v>2</v>
-      </c>
-      <c r="H111" t="str">
-        <v/>
-      </c>
-      <c r="I111" t="str">
-        <v/>
-      </c>
-      <c r="J111" t="str">
-        <v/>
-      </c>
-      <c r="K111" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>2026/08/27</v>
-      </c>
-      <c r="B112" t="str">
-        <v>20:30</v>
-      </c>
-      <c r="C112" t="str">
-        <v>EUR</v>
-      </c>
-      <c r="D112" t="str">
-        <v>유로 지역</v>
-      </c>
-      <c r="E112" t="str">
-        <v/>
-      </c>
-      <c r="F112" t="str">
-        <v>ECB 통화 정책 회의</v>
-      </c>
-      <c r="G112">
-        <v>2</v>
-      </c>
-      <c r="H112" t="str">
-        <v/>
-      </c>
-      <c r="I112" t="str">
-        <v/>
-      </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
-      <c r="K112" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>2026/08/27</v>
-      </c>
-      <c r="B113" t="str">
-        <v>21:30</v>
-      </c>
-      <c r="C113" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D113" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E113" t="str">
-        <v>2026/08/22</v>
-      </c>
-      <c r="F113" t="str">
-        <v>신규 실업수당 청구건수</v>
-      </c>
-      <c r="G113">
-        <v>2</v>
-      </c>
-      <c r="H113" t="str">
-        <v/>
-      </c>
-      <c r="I113" t="str">
-        <v>209K</v>
-      </c>
-      <c r="J113" t="str">
-        <v>210.0K</v>
-      </c>
-      <c r="K113" t="str">
-        <v>206K</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>2026/08/28</v>
-      </c>
-      <c r="B114" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="C114" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D114" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E114" t="str">
-        <v/>
-      </c>
-      <c r="F114" t="str">
-        <v>Jackson Hole 심포지엄</v>
-      </c>
-      <c r="G114">
-        <v>2</v>
-      </c>
-      <c r="H114" t="str">
-        <v/>
-      </c>
-      <c r="I114" t="str">
-        <v/>
-      </c>
-      <c r="J114" t="str">
-        <v/>
-      </c>
-      <c r="K114" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>2026/08/28</v>
-      </c>
-      <c r="B115" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="C115" t="str">
-        <v>EUR</v>
-      </c>
-      <c r="D115" t="str">
-        <v>유로 지역</v>
-      </c>
-      <c r="E115" t="str">
-        <v>2026/08/31</v>
-      </c>
-      <c r="F115" t="str">
-        <v>경제 심리지수</v>
-      </c>
-      <c r="G115">
-        <v>2</v>
-      </c>
-      <c r="H115" t="str">
-        <v/>
-      </c>
-      <c r="I115" t="str">
-        <v>97.5</v>
-      </c>
-      <c r="J115" t="str">
-        <v>97.7</v>
-      </c>
-      <c r="K115" t="str">
-        <v>96.9</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>2026/08/28</v>
-      </c>
-      <c r="B116" t="str">
-        <v>22:45</v>
-      </c>
-      <c r="C116" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D116" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E116" t="str">
-        <v>2026/08/31</v>
-      </c>
-      <c r="F116" t="str">
-        <v>시카고 PMI</v>
-      </c>
-      <c r="G116">
-        <v>2</v>
-      </c>
-      <c r="H116" t="str">
-        <v/>
-      </c>
-      <c r="I116" t="str">
-        <v>57</v>
-      </c>
-      <c r="J116" t="str">
-        <v>56.1</v>
-      </c>
-      <c r="K116" t="str">
-        <v>57.6</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>2026/08/28</v>
-      </c>
-      <c r="B117" t="str">
-        <v>23:00</v>
-      </c>
-      <c r="C117" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D117" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E117" t="str">
-        <v>2026/08/31</v>
-      </c>
-      <c r="F117" t="str">
-        <v>미시간대 Consumer Sentiment(확정)</v>
-      </c>
-      <c r="G117">
-        <v>2</v>
-      </c>
-      <c r="H117" t="str">
-        <v/>
-      </c>
-      <c r="I117" t="str">
-        <v>51.0</v>
-      </c>
-      <c r="J117" t="str">
-        <v>51.0</v>
-      </c>
-      <c r="K117" t="str">
-        <v>55.2</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>2026/08/29</v>
-      </c>
-      <c r="B118" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="C118" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D118" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E118" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v>Jackson Hole 심포지엄</v>
-      </c>
-      <c r="G118">
-        <v>2</v>
-      </c>
-      <c r="H118" t="str">
-        <v/>
-      </c>
-      <c r="I118" t="str">
-        <v/>
-      </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
-      <c r="K118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>2026/08/31</v>
-      </c>
-      <c r="B119" t="str">
-        <v>23:30</v>
-      </c>
-      <c r="C119" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D119" t="str">
-        <v>미국</v>
-      </c>
-      <c r="E119" t="str">
-        <v>2026/08/31</v>
-      </c>
-      <c r="F119" t="str">
-        <v>댈러스 연준 제조업지수</v>
-      </c>
-      <c r="G119">
-        <v>2</v>
-      </c>
-      <c r="H119" t="str">
-        <v/>
-      </c>
-      <c r="I119" t="str">
-        <v/>
-      </c>
-      <c r="J119" t="str">
-        <v>0.7</v>
-      </c>
-      <c r="K119" t="str">
-        <v>1.3</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/incoming/경제지표.xlsx
+++ b/incoming/경제지표.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K119"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
   </cols>
@@ -439,77 +439,77 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/03</v>
       </c>
       <c r="B2" t="str">
-        <v>18:00</v>
+        <v>22:45</v>
       </c>
       <c r="C2" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D2" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E2" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F2" t="str">
-        <v>CPI상승률(속보) YoY</v>
+        <v>S&amp;P 제조업 PMI(확정)</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>53.9</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>53.8</v>
       </c>
       <c r="J2" t="str">
-        <v>3.1%</v>
+        <v>53.8</v>
       </c>
       <c r="K2" t="str">
-        <v>2.9%</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/03</v>
       </c>
       <c r="B3" t="str">
-        <v>18:00</v>
+        <v>23:00</v>
       </c>
       <c r="C3" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D3" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E3" t="str">
         <v>2026/07/31</v>
       </c>
       <c r="F3" t="str">
-        <v>실업률</v>
+        <v>ISM 제조업 PMI</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>55.6</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>54</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>53.7</v>
       </c>
       <c r="K3" t="str">
-        <v>6.3%</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/03</v>
       </c>
       <c r="B4" t="str">
         <v>23:00</v>
@@ -521,33 +521,33 @@
         <v>미국</v>
       </c>
       <c r="E4" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F4" t="str">
-        <v>ISM 제조업 PMI</v>
+        <v>ISM 제조업 고용지수</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>52.8</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>55</v>
+        <v>49.8</v>
       </c>
       <c r="K4" t="str">
-        <v>55.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B5" t="str">
-        <v>23:00</v>
+        <v>04:00</v>
       </c>
       <c r="C5" t="str">
         <v>USD</v>
@@ -556,10 +556,10 @@
         <v>미국</v>
       </c>
       <c r="E5" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>ISM 제조업 고용지수</v>
+        <v>미 재무부 차환발행 자금조달 추정지</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -571,18 +571,18 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>52.5</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>52.8</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B6" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C6" t="str">
         <v>USD</v>
@@ -591,33 +591,33 @@
         <v>미국</v>
       </c>
       <c r="E6" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F6" t="str">
-        <v>JOLTs 구인 건수</v>
+        <v>수입</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>$388.0B</v>
       </c>
       <c r="I6" t="str">
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>7.32M</v>
+        <v>$ 385.0B</v>
       </c>
       <c r="K6" t="str">
-        <v>7.359M</v>
+        <v>$395.3B</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026/09/01</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B7" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C7" t="str">
         <v>USD</v>
@@ -626,33 +626,33 @@
         <v>미국</v>
       </c>
       <c r="E7" t="str">
-        <v>2026/09/30</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F7" t="str">
-        <v>RCM/TIPP 경제 낙관지수</v>
+        <v>무역수지</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>$-73.3B</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>$-73.0B</v>
       </c>
       <c r="J7" t="str">
-        <v>47</v>
+        <v>$ -73.0B</v>
       </c>
       <c r="K7" t="str">
-        <v>45.1</v>
+        <v>$-77.6B</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026/09/02</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B8" t="str">
-        <v>05:30</v>
+        <v>21:30</v>
       </c>
       <c r="C8" t="str">
         <v>USD</v>
@@ -661,33 +661,33 @@
         <v>미국</v>
       </c>
       <c r="E8" t="str">
-        <v>2026/08/28</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F8" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>수출</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>$314.7B</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>$312.0B</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>$317.6B</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026/09/02</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B9" t="str">
-        <v>21:15</v>
+        <v>23:00</v>
       </c>
       <c r="C9" t="str">
         <v>USD</v>
@@ -699,27 +699,27 @@
         <v>2026/08/31</v>
       </c>
       <c r="F9" t="str">
-        <v>ADP 고용 증감</v>
+        <v>RCM/TIPP 경제 낙관지수</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>45.1</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>47.5</v>
       </c>
       <c r="J9" t="str">
-        <v>59.0K</v>
+        <v>47</v>
       </c>
       <c r="K9" t="str">
-        <v>44K</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026/09/02</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B10" t="str">
         <v>23:00</v>
@@ -731,7 +731,7 @@
         <v>미국</v>
       </c>
       <c r="E10" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F10" t="str">
         <v>공장 주문 MoM</v>
@@ -740,24 +740,24 @@
         <v>2</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J10" t="str">
-        <v>-0.1%</v>
+        <v>0.4%</v>
       </c>
       <c r="K10" t="str">
-        <v>-0.3%</v>
+        <v>-1.1%</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026/09/02</v>
+        <v>2026/08/04</v>
       </c>
       <c r="B11" t="str">
-        <v>23:30</v>
+        <v>23:00</v>
       </c>
       <c r="C11" t="str">
         <v>USD</v>
@@ -766,33 +766,33 @@
         <v>미국</v>
       </c>
       <c r="E11" t="str">
-        <v>2026/08/28</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F11" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>JOLTs 구인 건수</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>7.359M</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>7.4M</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>7.3M</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>7.537M</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026/09/02</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B12" t="str">
-        <v>23:30</v>
+        <v>05:30</v>
       </c>
       <c r="C12" t="str">
         <v>USD</v>
@@ -801,33 +801,33 @@
         <v>미국</v>
       </c>
       <c r="E12" t="str">
-        <v>2026/08/28</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F12" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>2.69M</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>-2M</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>3.296M</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B13" t="str">
-        <v>21:30</v>
+        <v>21:15</v>
       </c>
       <c r="C13" t="str">
         <v>USD</v>
@@ -836,30 +836,30 @@
         <v>미국</v>
       </c>
       <c r="E13" t="str">
-        <v>2026/08/29</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F13" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>ADP 고용 증감</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>44K</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>70K</v>
       </c>
       <c r="J13" t="str">
-        <v>203.0K</v>
+        <v>90.0K</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>95K</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B14" t="str">
         <v>21:30</v>
@@ -871,10 +871,10 @@
         <v>미국</v>
       </c>
       <c r="E14" t="str">
-        <v>2026/06/30</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>단위 노동 비용(확정) QoQ</v>
+        <v>미 재무부 차환발행 발표</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -889,15 +889,15 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>1.8%</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B15" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C15" t="str">
         <v>USD</v>
@@ -909,30 +909,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F15" t="str">
-        <v>수입</v>
+        <v>S&amp;P 서비스업 PMI(확정)</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>54.6</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>53.6</v>
       </c>
       <c r="J15" t="str">
-        <v>$389.0B</v>
+        <v>53.6</v>
       </c>
       <c r="K15" t="str">
-        <v>$388.0B</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B16" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C16" t="str">
         <v>USD</v>
@@ -941,33 +941,33 @@
         <v>미국</v>
       </c>
       <c r="E16" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F16" t="str">
-        <v>비농업 생산성(확정) QoQ</v>
+        <v>S&amp;P 종합 PMI(확정)</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="I16" t="str">
-        <v>1.4%</v>
+        <v>53.6</v>
       </c>
       <c r="J16" t="str">
-        <v>1.4%</v>
+        <v>53.6</v>
       </c>
       <c r="K16" t="str">
-        <v>0.3%</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B17" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C17" t="str">
         <v>USD</v>
@@ -979,30 +979,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F17" t="str">
-        <v>수출</v>
+        <v>ISM 서비스업 PMI</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>54.1</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="J17" t="str">
-        <v>$315.0B</v>
+        <v>54.5</v>
       </c>
       <c r="K17" t="str">
-        <v>$314.7B</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B18" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C18" t="str">
         <v>USD</v>
@@ -1014,30 +1014,30 @@
         <v>2026/07/31</v>
       </c>
       <c r="F18" t="str">
-        <v>무역수지</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>-1.643M</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>-1.3M</v>
       </c>
       <c r="J18" t="str">
-        <v>$-74.0B</v>
+        <v/>
       </c>
       <c r="K18" t="str">
-        <v>$-73.3B</v>
+        <v>0.007M</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026/09/03</v>
+        <v>2026/08/05</v>
       </c>
       <c r="B19" t="str">
-        <v>23:00</v>
+        <v>23:30</v>
       </c>
       <c r="C19" t="str">
         <v>USD</v>
@@ -1046,45 +1046,45 @@
         <v>미국</v>
       </c>
       <c r="E19" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F19" t="str">
-        <v>ISM 서비스업 PMI</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>2.479M</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>-1.5M</v>
       </c>
       <c r="J19" t="str">
-        <v>53.8</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>54.1</v>
+        <v>-7.167M</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B20" t="str">
-        <v>18:00</v>
+        <v>05:05</v>
       </c>
       <c r="C20" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D20" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E20" t="str">
-        <v>2026/07/31</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>소매판매 MoM</v>
+        <v>Fed Cook 연설</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1099,47 +1099,47 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>-0.3%</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B21" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C21" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D21" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E21" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F21" t="str">
-        <v>시간당 평균 소득 MoM</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>-0.3%</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J21" t="str">
-        <v>0.2%</v>
+        <v>0.1%</v>
       </c>
       <c r="K21" t="str">
-        <v>0.1%</v>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B22" t="str">
         <v>21:30</v>
@@ -1151,30 +1151,30 @@
         <v>미국</v>
       </c>
       <c r="E22" t="str">
-        <v>2026/08/31</v>
+        <v>2026/08/01</v>
       </c>
       <c r="F22" t="str">
-        <v>비농업 고용자수</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>200K</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>202K</v>
       </c>
       <c r="J22" t="str">
-        <v>12.0K</v>
+        <v>199.0K</v>
       </c>
       <c r="K22" t="str">
-        <v>-23K</v>
+        <v>198K</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B23" t="str">
         <v>21:30</v>
@@ -1186,30 +1186,30 @@
         <v>미국</v>
       </c>
       <c r="E23" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F23" t="str">
-        <v>시간당 평균소득 YoY</v>
+        <v>단위 노동 비용(잠정) QoQ</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>1.3%</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2.1%</v>
       </c>
       <c r="J23" t="str">
-        <v>3.3%</v>
+        <v>2.0%</v>
       </c>
       <c r="K23" t="str">
-        <v>3.2%</v>
+        <v>1.3%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/06</v>
       </c>
       <c r="B24" t="str">
         <v>21:30</v>
@@ -1221,33 +1221,33 @@
         <v>미국</v>
       </c>
       <c r="E24" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F24" t="str">
-        <v>실업률</v>
+        <v>비농업 생산성(잠정) QoQ</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>1.4%</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>0.6%</v>
       </c>
       <c r="J24" t="str">
-        <v>4.2%</v>
+        <v>0.6%</v>
       </c>
       <c r="K24" t="str">
-        <v>4.1%</v>
+        <v>0.8%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026/09/04</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B25" t="str">
-        <v>21:30</v>
+        <v>06:30</v>
       </c>
       <c r="C25" t="str">
         <v>USD</v>
@@ -1256,10 +1256,10 @@
         <v>미국</v>
       </c>
       <c r="E25" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>참가율</v>
+        <v>Fed Musalem 연설</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1271,123 +1271,123 @@
         <v/>
       </c>
       <c r="J25" t="str">
-        <v>61.4%</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>61.4%</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026/09/07</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B26" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C26" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D26" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E26" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F26" t="str">
-        <v>GDP 성장률(3차 추정) YoY</v>
+        <v>참가율</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>61.4%</v>
       </c>
       <c r="I26" t="str">
-        <v>1%</v>
+        <v/>
       </c>
       <c r="J26" t="str">
-        <v>1.0%</v>
+        <v>61.6%</v>
       </c>
       <c r="K26" t="str">
-        <v>0.5%</v>
+        <v>61.5%</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026/09/07</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B27" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C27" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D27" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E27" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F27" t="str">
-        <v>고용 증감(확정) QoQ</v>
+        <v>비농업 고용자수</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>-23K</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>80K</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>79.0K</v>
       </c>
       <c r="K27" t="str">
-        <v>0.1%</v>
+        <v>20K</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026/09/07</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B28" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D28" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E28" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F28" t="str">
-        <v>GDP 성장률(3차 추정) QoQ</v>
+        <v>시간당 평균소득 YoY</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>3.2%</v>
       </c>
       <c r="I28" t="str">
-        <v>0.4%</v>
+        <v>3.5%</v>
       </c>
       <c r="J28" t="str">
-        <v>0.4%</v>
+        <v>3.5%</v>
       </c>
       <c r="K28" t="str">
-        <v>0.0%</v>
+        <v>3.4%</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026/09/08</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B29" t="str">
-        <v>21:15</v>
+        <v>21:30</v>
       </c>
       <c r="C29" t="str">
         <v>USD</v>
@@ -1396,33 +1396,33 @@
         <v>미국</v>
       </c>
       <c r="E29" t="str">
-        <v>2026/08/22</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F29" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>실업률</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>4.1%</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>4.2%</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B30" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C30" t="str">
         <v>USD</v>
@@ -1431,33 +1431,33 @@
         <v>미국</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F30" t="str">
-        <v>국채 입찰(10Y Note)</v>
+        <v>시간당 평균 소득 MoM</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/07</v>
       </c>
       <c r="B31" t="str">
-        <v>05:30</v>
+        <v>23:00</v>
       </c>
       <c r="C31" t="str">
         <v>USD</v>
@@ -1466,10 +1466,10 @@
         <v>미국</v>
       </c>
       <c r="E31" t="str">
-        <v>2026/09/04</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1489,25 +1489,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/09</v>
       </c>
       <c r="B32" t="str">
-        <v>21:15</v>
+        <v>01:45</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D32" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E32" t="str">
-        <v>2026/09/10</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v>ECB 금리결정</v>
+        <v>Fed Bowman 연설</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -1524,25 +1524,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B33" t="str">
-        <v>21:15</v>
+        <v>04:00</v>
       </c>
       <c r="C33" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D33" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E33" t="str">
-        <v>2026/09/10</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>예금 금리</v>
+        <v>Fed Hammack 연설</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1554,15 +1554,15 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>2.25%</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B34" t="str">
-        <v>21:30</v>
+        <v>21:15</v>
       </c>
       <c r="C34" t="str">
         <v>USD</v>
@@ -1571,16 +1571,16 @@
         <v>미국</v>
       </c>
       <c r="E34" t="str">
-        <v>2026/09/05</v>
+        <v>2026/07/25</v>
       </c>
       <c r="F34" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G34">
         <v>2</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>8.25K</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1589,15 +1589,15 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>11.0K</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B35" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C35" t="str">
         <v>USD</v>
@@ -1606,33 +1606,33 @@
         <v>미국</v>
       </c>
       <c r="E35" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F35" t="str">
-        <v>근원 PPI MoM</v>
+        <v>기존주택 판매</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>4.06M</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>4.05M</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>4.06M</v>
       </c>
       <c r="K35" t="str">
-        <v>0.2%</v>
+        <v>4.13M</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/11</v>
       </c>
       <c r="B36" t="str">
-        <v>21:30</v>
+        <v>23:00</v>
       </c>
       <c r="C36" t="str">
         <v>USD</v>
@@ -1641,68 +1641,68 @@
         <v>미국</v>
       </c>
       <c r="E36" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F36" t="str">
-        <v>PPI MoM</v>
+        <v>기존주택 판매 MoM</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>-1.7%</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>-0.7%</v>
       </c>
       <c r="K36" t="str">
-        <v>0%</v>
+        <v>-1.4%</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B37" t="str">
-        <v>21:45</v>
+        <v>05:30</v>
       </c>
       <c r="C37" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D37" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>2026/08/07</v>
       </c>
       <c r="F37" t="str">
-        <v>ECB 기자 회견</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>9.072M</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>-0.50M</v>
       </c>
       <c r="J37" t="str">
         <v/>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>2.69M</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B38" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C38" t="str">
         <v>USD</v>
@@ -1711,33 +1711,33 @@
         <v>미국</v>
       </c>
       <c r="E38" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F38" t="str">
-        <v>기존주택 판매</v>
+        <v>소비자물가지수-계절조정</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>332.81</v>
       </c>
       <c r="I38" t="str">
         <v/>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>332.6</v>
       </c>
       <c r="K38" t="str">
-        <v>4.06M</v>
+        <v>332.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026/09/10</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B39" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C39" t="str">
         <v>USD</v>
@@ -1746,33 +1746,33 @@
         <v>미국</v>
       </c>
       <c r="E39" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F39" t="str">
-        <v>기존주택 판매 MoM</v>
+        <v>CPI상승률 YoY</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>3.4%</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>3.4%</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>3.4%</v>
       </c>
       <c r="K39" t="str">
-        <v>-1.7%</v>
+        <v>3.5%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B40" t="str">
-        <v>01:00</v>
+        <v>21:30</v>
       </c>
       <c r="C40" t="str">
         <v>USD</v>
@@ -1781,33 +1781,33 @@
         <v>미국</v>
       </c>
       <c r="E40" t="str">
-        <v>2026/09/04</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F40" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>근원 CPI상승률 MoM</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>0%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B41" t="str">
-        <v>01:00</v>
+        <v>21:30</v>
       </c>
       <c r="C41" t="str">
         <v>USD</v>
@@ -1816,33 +1816,33 @@
         <v>미국</v>
       </c>
       <c r="E41" t="str">
-        <v>2026/09/04</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F41" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>근원 CPI상승률 YoY</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>2.6%</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B42" t="str">
-        <v>02:00</v>
+        <v>21:30</v>
       </c>
       <c r="C42" t="str">
         <v>USD</v>
@@ -1851,30 +1851,30 @@
         <v>미국</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>2026/07/31</v>
       </c>
       <c r="F42" t="str">
-        <v>국채 입찰(30Y Bond)</v>
+        <v>CPI상승률 MoM</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>0.0%</v>
       </c>
       <c r="K42" t="str">
-        <v>5.216%</v>
+        <v>-0.4%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B43" t="str">
         <v>21:30</v>
@@ -1886,33 +1886,33 @@
         <v>미국</v>
       </c>
       <c r="E43" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F43" t="str">
-        <v>근원 CPI상승률 MoM</v>
+        <v>소비자물가지수</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>333.92</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>333.99</v>
       </c>
       <c r="J43" t="str">
-        <v>0.2%</v>
+        <v>334.03</v>
       </c>
       <c r="K43" t="str">
-        <v>0.2%</v>
+        <v>333.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B44" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -1921,33 +1921,33 @@
         <v>미국</v>
       </c>
       <c r="E44" t="str">
-        <v>2026/08/31</v>
+        <v>2026/08/07</v>
       </c>
       <c r="F44" t="str">
-        <v>CPI상승률 YoY</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>-0.968M</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>-1.2M</v>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>3.4%</v>
+        <v>-1.643M</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/12</v>
       </c>
       <c r="B45" t="str">
-        <v>21:30</v>
+        <v>23:30</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -1956,33 +1956,33 @@
         <v>미국</v>
       </c>
       <c r="E45" t="str">
-        <v>2026/08/31</v>
+        <v>2026/08/07</v>
       </c>
       <c r="F45" t="str">
-        <v>CPI상승률 MoM</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>17.422M</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>-1.4M</v>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>0.1%</v>
+        <v>2.479M</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B46" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -1991,16 +1991,16 @@
         <v>미국</v>
       </c>
       <c r="E46" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>근원 CPI상승률 YoY</v>
+        <v>국채 입찰(10Y Note)</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>4.683%</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2009,15 +2009,15 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>2.5%</v>
+        <v>4.580%</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B47" t="str">
-        <v>21:30</v>
+        <v>03:00</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -2026,68 +2026,68 @@
         <v>미국</v>
       </c>
       <c r="E47" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F47" t="str">
-        <v>소비자물가지수</v>
+        <v>월간 예산 성명서</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>$-432B</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>$-346B</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>$-340.0B</v>
       </c>
       <c r="K47" t="str">
-        <v>333.92</v>
+        <v>$-120B</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B48" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C48" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D48" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E48" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F48" t="str">
-        <v>소비자물가지수-계절조정</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
       <c r="K48" t="str">
-        <v>332.81</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B49" t="str">
-        <v>23:00</v>
+        <v>21:15</v>
       </c>
       <c r="C49" t="str">
         <v>USD</v>
@@ -2096,10 +2096,10 @@
         <v>미국</v>
       </c>
       <c r="E49" t="str">
-        <v>2026/09/30</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>미시간대 Consumer Sentiment(잠정)</v>
+        <v>Fed Hammack 연설</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026/09/12</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B50" t="str">
-        <v>03:00</v>
+        <v>21:30</v>
       </c>
       <c r="C50" t="str">
         <v>USD</v>
@@ -2131,103 +2131,103 @@
         <v>미국</v>
       </c>
       <c r="E50" t="str">
-        <v>2026/08/31</v>
+        <v>2026/08/08</v>
       </c>
       <c r="F50" t="str">
-        <v>월간 예산 성명서</v>
+        <v>신규 실업수당 청구건수</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>212K</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>202K</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>204.0K</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>200K</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026/09/15</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B51" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C51" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D51" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E51" t="str">
-        <v>2026/09/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F51" t="str">
-        <v>ZEW 경제심리지수</v>
+        <v>근원 PPI MoM</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J51" t="str">
-        <v>5</v>
+        <v>0.2%</v>
       </c>
       <c r="K51" t="str">
-        <v>31.4</v>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026/09/15</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B52" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C52" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D52" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E52" t="str">
         <v>2026/07/31</v>
       </c>
       <c r="F52" t="str">
-        <v>무역수지</v>
+        <v>PPI MoM</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="K52" t="str">
-        <v>€8.6B</v>
+        <v>-0.1%</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026/09/15</v>
+        <v>2026/08/13</v>
       </c>
       <c r="B53" t="str">
-        <v>21:15</v>
+        <v>21:40</v>
       </c>
       <c r="C53" t="str">
         <v>USD</v>
@@ -2236,10 +2236,10 @@
         <v>미국</v>
       </c>
       <c r="E53" t="str">
-        <v>2026/08/29</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026/09/15</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B54" t="str">
-        <v>21:30</v>
+        <v>02:00</v>
       </c>
       <c r="C54" t="str">
         <v>USD</v>
@@ -2271,65 +2271,65 @@
         <v>미국</v>
       </c>
       <c r="E54" t="str">
-        <v>2026/09/30</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v>뉴욕 엠파이어스테이트 제조업지수</v>
+        <v>국채 입찰(30Y Bond)</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>5.216%</v>
       </c>
       <c r="I54" t="str">
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>-9</v>
+        <v/>
       </c>
       <c r="K54" t="str">
-        <v>20.60</v>
+        <v>5.058%</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B55" t="str">
-        <v>05:30</v>
+        <v>18:00</v>
       </c>
       <c r="C55" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D55" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E55" t="str">
-        <v>2026/09/11</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F55" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>GDP 성장률(2차 추정) QoQ</v>
       </c>
       <c r="G55">
         <v>2</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B56" t="str">
         <v>18:00</v>
@@ -2341,100 +2341,100 @@
         <v>유로 지역</v>
       </c>
       <c r="E56" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F56" t="str">
-        <v>산업생산 MoM</v>
+        <v>고용 증감(잠정) QoQ</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="K56" t="str">
-        <v>0%</v>
+        <v>0.1%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B57" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C57" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D57" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E57" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F57" t="str">
-        <v>수입가격 MoM</v>
+        <v>GDP 성장률(2차 추정) YoY</v>
       </c>
       <c r="G57">
         <v>2</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>1%</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>1%</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>1.0%</v>
       </c>
       <c r="K57" t="str">
-        <v>-0.4%</v>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B58" t="str">
-        <v>21:30</v>
+        <v>18:00</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D58" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E58" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F58" t="str">
-        <v>소매판매 MoM</v>
+        <v>무역수지</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>€8.6B</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>€-2.2B</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>€ 5B</v>
       </c>
       <c r="K58" t="str">
-        <v>-0.6%</v>
+        <v>€-9B</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B59" t="str">
         <v>21:30</v>
@@ -2446,30 +2446,30 @@
         <v>미국</v>
       </c>
       <c r="E59" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F59" t="str">
-        <v>수출가격 MoM</v>
+        <v>소매판매 MoM</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>-0.6%</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K59" t="str">
-        <v>-1.3%</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B60" t="str">
         <v>23:00</v>
@@ -2481,30 +2481,30 @@
         <v>미국</v>
       </c>
       <c r="E60" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F60" t="str">
-        <v>기업 재고 MoM</v>
+        <v>미시간대 Consumer Sentiment(잠정)</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>51.0</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>54.6</v>
       </c>
       <c r="K60" t="str">
-        <v>0%</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/14</v>
       </c>
       <c r="B61" t="str">
         <v>23:00</v>
@@ -2516,33 +2516,33 @@
         <v>미국</v>
       </c>
       <c r="E61" t="str">
-        <v>2026/09/30</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F61" t="str">
-        <v>NAHB 주택 시장지수</v>
+        <v>기업 재고 MoM</v>
       </c>
       <c r="G61">
         <v>2</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>0%</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J61" t="str">
-        <v>42</v>
+        <v>0.2%</v>
       </c>
       <c r="K61" t="str">
-        <v>35</v>
+        <v>0.4%</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/17</v>
       </c>
       <c r="B62" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C62" t="str">
         <v>USD</v>
@@ -2551,33 +2551,33 @@
         <v>미국</v>
       </c>
       <c r="E62" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F62" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>뉴욕 엠파이어스테이트 제조업지수</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>20.60</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>12</v>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>15.60</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026/09/16</v>
+        <v>2026/08/17</v>
       </c>
       <c r="B63" t="str">
-        <v>23:30</v>
+        <v>23:00</v>
       </c>
       <c r="C63" t="str">
         <v>USD</v>
@@ -2586,33 +2586,33 @@
         <v>미국</v>
       </c>
       <c r="E63" t="str">
-        <v>2026/09/11</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F63" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>NAHB 주택 시장지수</v>
       </c>
       <c r="G63">
         <v>2</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>35</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>33</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>34</v>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B64" t="str">
-        <v>03:00</v>
+        <v>05:00</v>
       </c>
       <c r="C64" t="str">
         <v>USD</v>
@@ -2621,68 +2621,68 @@
         <v>미국</v>
       </c>
       <c r="E64" t="str">
-        <v>2026/09/16</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F64" t="str">
-        <v>FED 금리결정(상단)</v>
+        <v>장기 TIC 순 유출입</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>$172.7B</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>$151.4B</v>
       </c>
       <c r="J64" t="str">
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>3.75%</v>
+        <v>$231.2B</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B65" t="str">
-        <v>03:30</v>
+        <v>18:00</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>2026/08/31</v>
       </c>
       <c r="F65" t="str">
-        <v>Fed 기자 회견</v>
+        <v>ZEW 경제심리지수</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>31.4</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>25.4</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>24</v>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>23.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B66" t="str">
-        <v>05:00</v>
+        <v>21:15</v>
       </c>
       <c r="C66" t="str">
         <v>USD</v>
@@ -2691,16 +2691,16 @@
         <v>미국</v>
       </c>
       <c r="E66" t="str">
-        <v>2026/07/31</v>
+        <v>2026/08/01</v>
       </c>
       <c r="F66" t="str">
-        <v>장기 TIC 순 유출입</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G66">
         <v>2</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>9.5K</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2709,47 +2709,47 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>$172.7B</v>
+        <v>8.25K</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B67" t="str">
-        <v>18:00</v>
+        <v>21:30</v>
       </c>
       <c r="C67" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D67" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E67" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F67" t="str">
-        <v>CPI상승률(확정) YoY</v>
+        <v>주택 착공 MoM</v>
       </c>
       <c r="G67">
         <v>2</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>-12.4%</v>
       </c>
       <c r="I67" t="str">
         <v/>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>-4.7%</v>
       </c>
       <c r="K67" t="str">
-        <v>2.9%</v>
+        <v>19.7%</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B68" t="str">
         <v>21:30</v>
@@ -2761,30 +2761,30 @@
         <v>미국</v>
       </c>
       <c r="E68" t="str">
-        <v>2026/09/12</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F68" t="str">
-        <v>신규 실업수당 청구건수</v>
+        <v>주택 착공</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>1.239M</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>1.35M</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>1.36M</v>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>1.415M</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B69" t="str">
         <v>21:30</v>
@@ -2796,30 +2796,30 @@
         <v>미국</v>
       </c>
       <c r="E69" t="str">
-        <v>2026/09/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F69" t="str">
-        <v>필라델피아 연준 제조업지수</v>
+        <v>수입가격 MoM</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>-0.4%</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J69" t="str">
-        <v>7</v>
+        <v>0.2%</v>
       </c>
       <c r="K69" t="str">
-        <v>47.4</v>
+        <v>-0.3%</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B70" t="str">
         <v>21:30</v>
@@ -2831,33 +2831,33 @@
         <v>미국</v>
       </c>
       <c r="E70" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F70" t="str">
-        <v>주택 착공</v>
+        <v>수출가격 MoM</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>-1.3%</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J70" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K70" t="str">
-        <v>1.239M</v>
+        <v>-0.7%</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B71" t="str">
-        <v>21:30</v>
+        <v>22:15</v>
       </c>
       <c r="C71" t="str">
         <v>USD</v>
@@ -2866,30 +2866,30 @@
         <v>미국</v>
       </c>
       <c r="E71" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F71" t="str">
-        <v>주택 착공 MoM</v>
+        <v>산업생산 MoM</v>
       </c>
       <c r="G71">
         <v>2</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K71" t="str">
-        <v>-12.4%</v>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B72" t="str">
         <v>23:00</v>
@@ -2901,7 +2901,7 @@
         <v>미국</v>
       </c>
       <c r="E72" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F72" t="str">
         <v>잠정 주택 판매 MoM</v>
@@ -2910,21 +2910,21 @@
         <v>2</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>-2.3%</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>0.9%</v>
       </c>
       <c r="K72" t="str">
-        <v>-2.3%</v>
+        <v>-4.8%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026/09/17</v>
+        <v>2026/08/18</v>
       </c>
       <c r="B73" t="str">
         <v>23:00</v>
@@ -2936,7 +2936,7 @@
         <v>미국</v>
       </c>
       <c r="E73" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F73" t="str">
         <v>잠정주택 판매 YoY</v>
@@ -2945,24 +2945,24 @@
         <v>2</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>-2.2%</v>
       </c>
       <c r="I73" t="str">
         <v/>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>1.4%</v>
       </c>
       <c r="K73" t="str">
-        <v>-2.2%</v>
+        <v>-0.3%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026/09/18</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B74" t="str">
-        <v>22:15</v>
+        <v>06:00</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -2971,16 +2971,16 @@
         <v>미국</v>
       </c>
       <c r="E74" t="str">
-        <v>2026/08/31</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F74" t="str">
-        <v>산업생산 MoM</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>-0.328M</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2989,27 +2989,27 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>0.2%</v>
+        <v>9.072M</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026/09/21</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B75" t="str">
-        <v>21:30</v>
+        <v>16:10</v>
       </c>
       <c r="C75" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D75" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E75" t="str">
-        <v>2026/08/31</v>
+        <v/>
       </c>
       <c r="F75" t="str">
-        <v>시카고 연준 국가 활동지수</v>
+        <v>ECB 총재 Lagarde 연설</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -3029,45 +3029,45 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026/09/22</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B76" t="str">
-        <v>21:15</v>
+        <v>18:00</v>
       </c>
       <c r="C76" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D76" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E76" t="str">
-        <v>2026/09/05</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F76" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>CPI상승률(확정) YoY</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>2.9%</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>2.9%</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>2.9%</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>2.8%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026/09/23</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B77" t="str">
-        <v>05:30</v>
+        <v>23:30</v>
       </c>
       <c r="C77" t="str">
         <v>USD</v>
@@ -3076,30 +3076,30 @@
         <v>미국</v>
       </c>
       <c r="E77" t="str">
-        <v>2026/09/18</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F77" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>EIA 원유 재고 증감</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>4.405M</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>-0.6M</v>
       </c>
       <c r="J77" t="str">
         <v/>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>17.422M</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026/09/23</v>
+        <v>2026/08/19</v>
       </c>
       <c r="B78" t="str">
         <v>23:30</v>
@@ -3111,33 +3111,33 @@
         <v>미국</v>
       </c>
       <c r="E78" t="str">
-        <v>2026/09/18</v>
+        <v>2026/08/14</v>
       </c>
       <c r="F78" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>EIA 휘발유 재고 변동</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>0.688M</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>-1.2M</v>
       </c>
       <c r="J78" t="str">
         <v/>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>-0.968M</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2026/09/23</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B79" t="str">
-        <v>23:30</v>
+        <v>03:00</v>
       </c>
       <c r="C79" t="str">
         <v>USD</v>
@@ -3146,13 +3146,13 @@
         <v>미국</v>
       </c>
       <c r="E79" t="str">
-        <v>2026/09/18</v>
+        <v/>
       </c>
       <c r="F79" t="str">
-        <v>EIA 휘발유 재고 변동</v>
+        <v>FOMC 회의록</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026/09/24</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B80" t="str">
-        <v>02:00</v>
+        <v>20:30</v>
       </c>
       <c r="C80" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D80" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>국채 입찰(2년 FRN)</v>
+        <v>ECB 통화 정책 회의</v>
       </c>
       <c r="G80">
         <v>2</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026/09/24</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B81" t="str">
         <v>21:30</v>
@@ -3216,7 +3216,7 @@
         <v>미국</v>
       </c>
       <c r="E81" t="str">
-        <v>2026/09/19</v>
+        <v>2026/08/15</v>
       </c>
       <c r="F81" t="str">
         <v>신규 실업수당 청구건수</v>
@@ -3225,21 +3225,21 @@
         <v>2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>206K</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>210K</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>201.0K</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>212K</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2026/09/24</v>
+        <v>2026/08/20</v>
       </c>
       <c r="B82" t="str">
         <v>21:30</v>
@@ -3251,68 +3251,68 @@
         <v>미국</v>
       </c>
       <c r="E82" t="str">
-        <v>2026/06/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F82" t="str">
-        <v>경상수지</v>
+        <v>필라델피아 연준 제조업지수</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>47.4</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="J82" t="str">
-        <v>$ -220B</v>
+        <v>25</v>
       </c>
       <c r="K82" t="str">
-        <v>$-226.8B</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2026/09/24</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B83" t="str">
-        <v>23:00</v>
+        <v>18:00</v>
       </c>
       <c r="C83" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D83" t="str">
-        <v>미국</v>
+        <v>유로 지역</v>
       </c>
       <c r="E83" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F83" t="str">
-        <v>신규주택 판매</v>
+        <v>협상 임금 인상률</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>2.44%</v>
       </c>
       <c r="I83" t="str">
         <v/>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>2.5%</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>2.56%</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2026/09/24</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B84" t="str">
-        <v>23:00</v>
+        <v>22:45</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -3324,30 +3324,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F84" t="str">
-        <v>신규주택 판매 MoM</v>
+        <v>S&amp;P 서비스업 PMI(속보)</v>
       </c>
       <c r="G84">
         <v>2</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>56.8</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>54</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>53.8</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>54.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2026/09/25</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B85" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -3359,30 +3359,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F85" t="str">
-        <v>내구재 주문 MoM</v>
+        <v>S&amp;P 제조업 PMI(속보)</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>53.2</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>53.9</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>53.5</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>53.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2026/09/25</v>
+        <v>2026/08/21</v>
       </c>
       <c r="B86" t="str">
-        <v>21:30</v>
+        <v>22:45</v>
       </c>
       <c r="C86" t="str">
         <v>USD</v>
@@ -3394,30 +3394,30 @@
         <v>2026/08/31</v>
       </c>
       <c r="F86" t="str">
-        <v>내구재 주문(운송 제외) MoM</v>
+        <v>S&amp;P 종합 PMI(속보)</v>
       </c>
       <c r="G86">
         <v>2</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>56.0</v>
       </c>
       <c r="I86" t="str">
         <v/>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>53.2</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>54.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2026/09/25</v>
+        <v>2026/08/24</v>
       </c>
       <c r="B87" t="str">
-        <v>23:00</v>
+        <v>21:30</v>
       </c>
       <c r="C87" t="str">
         <v>USD</v>
@@ -3426,33 +3426,33 @@
         <v>미국</v>
       </c>
       <c r="E87" t="str">
-        <v>2026/09/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F87" t="str">
-        <v>미시간대 Consumer Sentiment(확정)</v>
+        <v>시카고 연준 국가 활동지수</v>
       </c>
       <c r="G87">
         <v>2</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>-0.08</v>
       </c>
       <c r="I87" t="str">
         <v/>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>0.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2026/09/28</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B88" t="str">
-        <v>23:30</v>
+        <v>21:00</v>
       </c>
       <c r="C88" t="str">
         <v>USD</v>
@@ -3461,10 +3461,10 @@
         <v>미국</v>
       </c>
       <c r="E88" t="str">
-        <v>2026/09/30</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v>댈러스 연준 제조업지수</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -3484,45 +3484,45 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B89" t="str">
-        <v>18:00</v>
+        <v>21:15</v>
       </c>
       <c r="C89" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D89" t="str">
-        <v>유로 지역</v>
+        <v>미국</v>
       </c>
       <c r="E89" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/08</v>
       </c>
       <c r="F89" t="str">
-        <v>경제 심리지수</v>
+        <v>ADP 고용 증감(4주 평균)</v>
       </c>
       <c r="G89">
         <v>2</v>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>11.75K</v>
       </c>
       <c r="I89" t="str">
         <v/>
       </c>
       <c r="J89" t="str">
-        <v>94.5</v>
+        <v/>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>9.5K</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B90" t="str">
-        <v>21:15</v>
+        <v>22:00</v>
       </c>
       <c r="C90" t="str">
         <v>USD</v>
@@ -3531,30 +3531,30 @@
         <v>미국</v>
       </c>
       <c r="E90" t="str">
-        <v>2026/09/12</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F90" t="str">
-        <v>ADP 고용 증감(4주 평균)</v>
+        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
       </c>
       <c r="G90">
         <v>2</v>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>2.1%</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>1.7%</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>1.8%</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>1.6%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B91" t="str">
         <v>22:00</v>
@@ -3566,7 +3566,7 @@
         <v>미국</v>
       </c>
       <c r="E91" t="str">
-        <v>2026/07/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F91" t="str">
         <v>S&amp;P/Case-Shiller 주택가격 MoM</v>
@@ -3575,24 +3575,24 @@
         <v>2</v>
       </c>
       <c r="H91" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>0.9%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B92" t="str">
-        <v>22:00</v>
+        <v>23:00</v>
       </c>
       <c r="C92" t="str">
         <v>USD</v>
@@ -3604,27 +3604,27 @@
         <v>2026/07/31</v>
       </c>
       <c r="F92" t="str">
-        <v>S&amp;P/Case-Shiller 주택가격 YoY</v>
+        <v>신규주택 판매</v>
       </c>
       <c r="G92">
         <v>2</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>0.607M</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>0.62M</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>0.62M</v>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>0.678M</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B93" t="str">
         <v>23:00</v>
@@ -3636,30 +3636,30 @@
         <v>미국</v>
       </c>
       <c r="E93" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F93" t="str">
-        <v>JOLTs 구인 건수</v>
+        <v>신규주택 판매 MoM</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>-10.5%</v>
       </c>
       <c r="I93" t="str">
         <v/>
       </c>
       <c r="J93" t="str">
-        <v/>
+        <v>-1.3%</v>
       </c>
       <c r="K93" t="str">
-        <v/>
+        <v>7.6%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2026/09/29</v>
+        <v>2026/08/25</v>
       </c>
       <c r="B94" t="str">
         <v>23:00</v>
@@ -3671,7 +3671,7 @@
         <v>미국</v>
       </c>
       <c r="E94" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/31</v>
       </c>
       <c r="F94" t="str">
         <v>CB 소비자 신뢰지수</v>
@@ -3680,24 +3680,24 @@
         <v>2</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>89.4</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>90.2</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>90.9</v>
       </c>
       <c r="K94" t="str">
-        <v/>
+        <v>90.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B95" t="str">
-        <v>05:30</v>
+        <v>05:00</v>
       </c>
       <c r="C95" t="str">
         <v>USD</v>
@@ -3706,10 +3706,10 @@
         <v>미국</v>
       </c>
       <c r="E95" t="str">
-        <v>2026/09/25</v>
+        <v/>
       </c>
       <c r="F95" t="str">
-        <v>API 원유 재고 변동</v>
+        <v>Fed Barkin 연설</v>
       </c>
       <c r="G95">
         <v>2</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B96" t="str">
-        <v>21:15</v>
+        <v>07:00</v>
       </c>
       <c r="C96" t="str">
         <v>USD</v>
@@ -3741,30 +3741,30 @@
         <v>미국</v>
       </c>
       <c r="E96" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/21</v>
       </c>
       <c r="F96" t="str">
-        <v>ADP 고용 증감</v>
+        <v>API 원유 재고 변동</v>
       </c>
       <c r="G96">
         <v>2</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>4.2M</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>1.8M</v>
       </c>
       <c r="J96" t="str">
-        <v>75K</v>
+        <v/>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>-0.328M</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B97" t="str">
         <v>21:30</v>
@@ -3776,30 +3776,30 @@
         <v>미국</v>
       </c>
       <c r="E97" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F97" t="str">
-        <v>PCE 물가지수 MoM</v>
+        <v>개인 지출 MoM</v>
       </c>
       <c r="G97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J97" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B98" t="str">
         <v>21:30</v>
@@ -3811,30 +3811,30 @@
         <v>미국</v>
       </c>
       <c r="E98" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F98" t="str">
-        <v>근원 PCE 물가지수 MoM</v>
+        <v>기업 이익(잠정) QoQ</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" t="str">
-        <v/>
+        <v>8.2%</v>
       </c>
       <c r="I98" t="str">
         <v/>
       </c>
       <c r="J98" t="str">
-        <v/>
+        <v>0.7%</v>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B99" t="str">
         <v>21:30</v>
@@ -3846,30 +3846,30 @@
         <v>미국</v>
       </c>
       <c r="E99" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F99" t="str">
-        <v>GDP성장률(3차 예측) QoQ</v>
+        <v>개인 소득 MoM</v>
       </c>
       <c r="G99">
         <v>3</v>
       </c>
       <c r="H99" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K99" t="str">
-        <v>2.1%</v>
+        <v>0.2%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B100" t="str">
         <v>21:30</v>
@@ -3881,30 +3881,30 @@
         <v>미국</v>
       </c>
       <c r="E100" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F100" t="str">
-        <v>기업 이익(확정) QoQ</v>
+        <v>PCE 물가지수 MoM</v>
       </c>
       <c r="G100">
         <v>2</v>
       </c>
       <c r="H100" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
       <c r="J100" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="K100" t="str">
-        <v/>
+        <v>-0.1%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B101" t="str">
         <v>21:30</v>
@@ -3916,30 +3916,30 @@
         <v>미국</v>
       </c>
       <c r="E101" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F101" t="str">
-        <v>PCE 물가지수 YoY</v>
+        <v>내구재 주문(운송 제외) MoM</v>
       </c>
       <c r="G101">
         <v>2</v>
       </c>
       <c r="H101" t="str">
-        <v/>
+        <v>0.4%</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>0.6%</v>
       </c>
       <c r="J101" t="str">
-        <v/>
+        <v>0.3%</v>
       </c>
       <c r="K101" t="str">
-        <v/>
+        <v>1.1%</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B102" t="str">
         <v>21:30</v>
@@ -3951,30 +3951,30 @@
         <v>미국</v>
       </c>
       <c r="E102" t="str">
-        <v>2026/06/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F102" t="str">
-        <v>GDP 물가지수(3차 예측) QoQ</v>
+        <v>내구재 주문 MoM</v>
       </c>
       <c r="G102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H102" t="str">
-        <v/>
+        <v>1.1%</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>0.5%</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>0.5%</v>
       </c>
       <c r="K102" t="str">
-        <v>3.6%</v>
+        <v>0.5%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B103" t="str">
         <v>21:30</v>
@@ -3986,30 +3986,30 @@
         <v>미국</v>
       </c>
       <c r="E103" t="str">
-        <v>2026/08/31</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F103" t="str">
-        <v>개인 지출 MoM</v>
+        <v>GDP 물가지수(2차 예측) QoQ</v>
       </c>
       <c r="G103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H103" t="str">
-        <v/>
+        <v>6.4%</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>6.3%</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>6.3%</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>3.6%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B104" t="str">
         <v>21:30</v>
@@ -4021,33 +4021,33 @@
         <v>미국</v>
       </c>
       <c r="E104" t="str">
-        <v>2026/08/31</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F104" t="str">
-        <v>개인 소득 MoM</v>
+        <v>PCE 물가지수 YoY</v>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H104" t="str">
-        <v/>
+        <v>3.7%</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>3.6%</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>3.7%</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>3.7%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B105" t="str">
-        <v>22:45</v>
+        <v>21:30</v>
       </c>
       <c r="C105" t="str">
         <v>USD</v>
@@ -4056,33 +4056,33 @@
         <v>미국</v>
       </c>
       <c r="E105" t="str">
-        <v>2026/09/30</v>
+        <v>2026/07/31</v>
       </c>
       <c r="F105" t="str">
-        <v>시카고 PMI</v>
+        <v>근원 PCE 물가지수 MoM</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>0.2%</v>
       </c>
       <c r="J105" t="str">
-        <v>55.9</v>
+        <v>0.3%</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>0.1%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B106" t="str">
-        <v>23:30</v>
+        <v>21:30</v>
       </c>
       <c r="C106" t="str">
         <v>USD</v>
@@ -4091,30 +4091,30 @@
         <v>미국</v>
       </c>
       <c r="E106" t="str">
-        <v>2026/09/25</v>
+        <v>2026/06/30</v>
       </c>
       <c r="F106" t="str">
-        <v>EIA 원유 재고 증감</v>
+        <v>GDP성장률(2차 예측) QoQ</v>
       </c>
       <c r="G106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" t="str">
-        <v/>
+        <v>1.5%</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>1.5%</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>1.5%</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>2.1%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2026/09/30</v>
+        <v>2026/08/26</v>
       </c>
       <c r="B107" t="str">
         <v>23:30</v>
@@ -4126,30 +4126,450 @@
         <v>미국</v>
       </c>
       <c r="E107" t="str">
-        <v>2026/09/25</v>
+        <v>2026/08/21</v>
       </c>
       <c r="F107" t="str">
+        <v>EIA 원유 재고 증감</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="H107" t="str">
+        <v>0.095M</v>
+      </c>
+      <c r="I107" t="str">
+        <v>0.6M</v>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v>4.405M</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026/08/26</v>
+      </c>
+      <c r="B108" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C108" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D108" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026/08/21</v>
+      </c>
+      <c r="F108" t="str">
         <v>EIA 휘발유 재고 변동</v>
       </c>
-      <c r="G107">
-        <v>2</v>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-      <c r="I107" t="str">
-        <v/>
-      </c>
-      <c r="J107" t="str">
-        <v/>
-      </c>
-      <c r="K107" t="str">
-        <v/>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108" t="str">
+        <v>-2.536M</v>
+      </c>
+      <c r="I108" t="str">
+        <v>-0.7M</v>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v>0.688M</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B109" t="str">
+        <v>00:30</v>
+      </c>
+      <c r="C109" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D109" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>국채 입찰(2년 FRN)</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109" t="str">
+        <v>0.055%</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v>0.050%</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B110" t="str">
+        <v>00:45</v>
+      </c>
+      <c r="C110" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D110" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>Fed Barkin 연설</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B111" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C111" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D111" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B112" t="str">
+        <v>20:30</v>
+      </c>
+      <c r="C112" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="D112" t="str">
+        <v>유로 지역</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>ECB 통화 정책 회의</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026/08/27</v>
+      </c>
+      <c r="B113" t="str">
+        <v>21:30</v>
+      </c>
+      <c r="C113" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D113" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026/08/22</v>
+      </c>
+      <c r="F113" t="str">
+        <v>신규 실업수당 청구건수</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v>208K</v>
+      </c>
+      <c r="J113" t="str">
+        <v>210.0K</v>
+      </c>
+      <c r="K113" t="str">
+        <v>206K</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B114" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C114" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D114" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G114">
+        <v>2</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B115" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C115" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="D115" t="str">
+        <v>유로 지역</v>
+      </c>
+      <c r="E115" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F115" t="str">
+        <v>경제 심리지수</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v>97.5</v>
+      </c>
+      <c r="J115" t="str">
+        <v>97.1</v>
+      </c>
+      <c r="K115" t="str">
+        <v>96.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B116" t="str">
+        <v>22:45</v>
+      </c>
+      <c r="C116" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D116" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F116" t="str">
+        <v>시카고 PMI</v>
+      </c>
+      <c r="G116">
+        <v>2</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>57</v>
+      </c>
+      <c r="J116" t="str">
+        <v>56.1</v>
+      </c>
+      <c r="K116" t="str">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026/08/28</v>
+      </c>
+      <c r="B117" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="C117" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D117" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F117" t="str">
+        <v>미시간대 Consumer Sentiment(확정)</v>
+      </c>
+      <c r="G117">
+        <v>2</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>51.0</v>
+      </c>
+      <c r="J117" t="str">
+        <v>51.0</v>
+      </c>
+      <c r="K117" t="str">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026/08/29</v>
+      </c>
+      <c r="B118" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="C118" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D118" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>Jackson Hole 심포지엄</v>
+      </c>
+      <c r="G118">
+        <v>2</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="B119" t="str">
+        <v>23:30</v>
+      </c>
+      <c r="C119" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D119" t="str">
+        <v>미국</v>
+      </c>
+      <c r="E119" t="str">
+        <v>2026/08/31</v>
+      </c>
+      <c r="F119" t="str">
+        <v>댈러스 연준 제조업지수</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="K119" t="str">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K119"/>
   </ignoredErrors>
 </worksheet>
 </file>